--- a/GPU32.xlsx
+++ b/GPU32.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="v2r4_instructions" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="298">
   <si>
     <t xml:space="preserve">INSTRUCTION FORMATS</t>
   </si>
@@ -472,6 +472,9 @@
     <t>ARG0</t>
   </si>
   <si>
+    <t>SUBSAT</t>
+  </si>
+  <si>
     <t>ARG1</t>
   </si>
   <si>
@@ -484,25 +487,16 @@
     <t>MUL</t>
   </si>
   <si>
-    <t>ABS</t>
-  </si>
-  <si>
     <t>ARG4</t>
   </si>
   <si>
     <t>MULH</t>
   </si>
   <si>
-    <t>MIN</t>
-  </si>
-  <si>
     <t>ARG5</t>
   </si>
   <si>
     <t>DIV</t>
-  </si>
-  <si>
-    <t>MAX</t>
   </si>
   <si>
     <t>ARG6</t>
@@ -518,6 +512,15 @@
   </si>
   <si>
     <t>POPCNT</t>
+  </si>
+  <si>
+    <t>ABS</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>MAX</t>
   </si>
   <si>
     <t>SYSTEM</t>
@@ -577,6 +580,9 @@
     <t>LERP</t>
   </si>
   <si>
+    <t>AVG</t>
+  </si>
+  <si>
     <t>BROADCAST</t>
   </si>
   <si>
@@ -584,9 +590,6 @@
   </si>
   <si>
     <t xml:space="preserve">Send interrupt to CPU</t>
-  </si>
-  <si>
-    <t>val</t>
   </si>
   <si>
     <t>LANES</t>
@@ -604,16 +607,25 @@
     <t>PCNT</t>
   </si>
   <si>
-    <t>UNPACK</t>
+    <t>val</t>
   </si>
   <si>
-    <t>SIMD</t>
+    <t>RGB565.UNPACK</t>
   </si>
   <si>
     <t>3x8</t>
   </si>
   <si>
-    <t>PACK</t>
+    <t xml:space="preserve">Top Byte is 0xFF if r0 is used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It is the top byte inverted</t>
+  </si>
+  <si>
+    <t>RGB565.PACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top Word is 0x00</t>
   </si>
   <si>
     <t xml:space="preserve">Pipeline test</t>
@@ -1097,7 +1109,7 @@
     <xf fontId="4" fillId="13" borderId="2" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1"/>
     <xf fontId="5" fillId="14" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="4" fillId="0" borderId="2" numFmtId="0" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1168,9 +1180,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="2" applyFill="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="8" borderId="0" numFmtId="0" xfId="7" applyFill="1"/>
     <xf fontId="2" fillId="9" borderId="0" numFmtId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -16724,9 +16743,11 @@
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
+      <c r="K34" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="L34" s="27"/>
+      <c r="M34" s="27"/>
       <c r="N34" s="3"/>
       <c r="T34" s="6"/>
       <c r="U34" s="6"/>
@@ -16747,7 +16768,7 @@
         <v>1</v>
       </c>
       <c r="AD34" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AE34" s="6"/>
       <c r="AF34" s="6"/>
@@ -16774,7 +16795,7 @@
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
+      <c r="K35" s="28"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="3"/>
@@ -16797,7 +16818,7 @@
         <v>0</v>
       </c>
       <c r="AD35" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE35" s="6"/>
       <c r="AF35" s="6"/>
@@ -16847,7 +16868,7 @@
         <v>1</v>
       </c>
       <c r="AD36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AE36" s="6"/>
       <c r="AF36" s="6"/>
@@ -16872,13 +16893,11 @@
         <v>0</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
-      <c r="K37" s="6" t="s">
-        <v>154</v>
-      </c>
+      <c r="K37" s="6"/>
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
       <c r="N37" s="3"/>
@@ -16931,9 +16950,7 @@
       </c>
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
-      <c r="K38" s="6" t="s">
-        <v>157</v>
-      </c>
+      <c r="K38" s="6"/>
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
       <c r="N38" s="3"/>
@@ -16956,7 +16973,7 @@
         <v>1</v>
       </c>
       <c r="AD38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AE38" s="6"/>
       <c r="AF38" s="6"/>
@@ -16981,13 +16998,11 @@
         <v>0</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I39" s="6"/>
       <c r="J39" s="6"/>
-      <c r="K39" s="6" t="s">
-        <v>160</v>
-      </c>
+      <c r="K39" s="6"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
       <c r="N39" s="3"/>
@@ -17011,7 +17026,7 @@
         <v>0</v>
       </c>
       <c r="AD39" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AE39" s="6"/>
       <c r="AF39" s="6"/>
@@ -17036,7 +17051,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
@@ -17066,7 +17081,7 @@
         <v>1</v>
       </c>
       <c r="AD40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AN40" s="3"/>
       <c r="AY40" s="3"/>
@@ -17087,7 +17102,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="25" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F41" s="25"/>
       <c r="G41" s="25"/>
@@ -17133,7 +17148,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
@@ -17178,6 +17193,9 @@
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
+      <c r="K43" t="s">
+        <v>164</v>
+      </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
@@ -17219,6 +17237,9 @@
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
+      <c r="K44" t="s">
+        <v>165</v>
+      </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
@@ -17260,6 +17281,9 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
+      <c r="K45" t="s">
+        <v>166</v>
+      </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3"/>
@@ -17269,7 +17293,7 @@
       <c r="T45" s="6"/>
       <c r="U45" s="6"/>
       <c r="V45" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="W45" s="12"/>
       <c r="X45" s="12"/>
@@ -17301,12 +17325,12 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="6"/>
       <c r="N46" s="20"/>
-      <c r="O46" s="3"/>
+      <c r="O46" s="20"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3"/>
@@ -17326,7 +17350,7 @@
       <c r="AF46" s="3"/>
       <c r="AV46" s="6"/>
       <c r="AX46" s="6"/>
-      <c r="AY46" s="27"/>
+      <c r="AY46" s="29"/>
     </row>
     <row r="47" ht="14.25">
       <c r="A47" s="5"/>
@@ -17343,12 +17367,12 @@
         <v>1</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
       <c r="N47" s="20"/>
-      <c r="O47" s="3"/>
+      <c r="O47" s="20"/>
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
@@ -17374,17 +17398,17 @@
         <v>0</v>
       </c>
       <c r="AB47" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC47" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AD47" s="20"/>
       <c r="AE47" s="3"/>
       <c r="AF47" s="3"/>
       <c r="AV47" s="6"/>
       <c r="AX47" s="6"/>
-      <c r="AY47" s="27"/>
+      <c r="AY47" s="29"/>
     </row>
     <row r="48" ht="14.25">
       <c r="A48" s="5"/>
@@ -17401,12 +17425,12 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
-      <c r="N48" s="3"/>
-      <c r="O48" s="3"/>
+      <c r="N48" s="20"/>
+      <c r="O48" s="20"/>
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
@@ -17434,7 +17458,7 @@
       <c r="AF48" s="3"/>
       <c r="AV48" s="6"/>
       <c r="AX48" s="6"/>
-      <c r="AY48" s="27"/>
+      <c r="AY48" s="29"/>
     </row>
     <row r="49" ht="14.25">
       <c r="A49" s="5"/>
@@ -17453,7 +17477,6 @@
       <c r="H49" s="6"/>
       <c r="I49" s="6"/>
       <c r="J49" s="6"/>
-      <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
       <c r="Q49" s="3"/>
@@ -17478,14 +17501,14 @@
         <v>0</v>
       </c>
       <c r="AB49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AD49" s="3"/>
       <c r="AE49" s="6"/>
       <c r="AF49" s="3"/>
       <c r="AV49" s="6"/>
       <c r="AX49" s="6"/>
-      <c r="AY49" s="27"/>
+      <c r="AY49" s="29"/>
     </row>
     <row r="50" ht="14.25">
       <c r="A50" s="12">
@@ -17535,7 +17558,7 @@
       <c r="AE50" s="6"/>
       <c r="AF50" s="3"/>
       <c r="AX50" s="6"/>
-      <c r="AY50" s="27"/>
+      <c r="AY50" s="29"/>
     </row>
     <row r="51" ht="14.25">
       <c r="A51" s="5"/>
@@ -17555,7 +17578,7 @@
       <c r="I51" s="6"/>
       <c r="J51" s="6"/>
       <c r="K51" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3"/>
@@ -17582,7 +17605,7 @@
       </c>
       <c r="AF51" s="3"/>
       <c r="AX51" s="6"/>
-      <c r="AY51" s="27"/>
+      <c r="AY51" s="29"/>
     </row>
     <row r="52" ht="14.25">
       <c r="A52" s="5"/>
@@ -17602,20 +17625,20 @@
       <c r="I52" s="6"/>
       <c r="J52" s="6"/>
       <c r="K52" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M52" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N52" s="6"/>
       <c r="O52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P52" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
@@ -17639,7 +17662,7 @@
       <c r="AB52" s="3"/>
       <c r="AF52" s="3"/>
       <c r="AX52" s="6"/>
-      <c r="AY52" s="27"/>
+      <c r="AY52" s="29"/>
     </row>
     <row r="53" ht="14.25">
       <c r="A53" s="5"/>
@@ -17659,13 +17682,13 @@
       <c r="I53" s="6"/>
       <c r="J53" s="6"/>
       <c r="K53" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L53" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O53" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
@@ -17710,10 +17733,10 @@
       <c r="I54" s="6"/>
       <c r="J54" s="6"/>
       <c r="K54" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L54" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
@@ -17758,7 +17781,7 @@
       <c r="I55" s="6"/>
       <c r="J55" s="6"/>
       <c r="K55" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
@@ -17805,6 +17828,9 @@
       <c r="H56" s="6"/>
       <c r="I56" s="6"/>
       <c r="J56" s="6"/>
+      <c r="K56" t="s">
+        <v>186</v>
+      </c>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
@@ -17989,7 +18015,7 @@
       <c r="I60" s="6"/>
       <c r="J60" s="6"/>
       <c r="K60" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
@@ -18250,10 +18276,10 @@
         <v>0</v>
       </c>
       <c r="AB65" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AD65" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AE65" s="3"/>
       <c r="AF65" s="3"/>
@@ -18461,9 +18487,12 @@
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
-      <c r="N70" s="3"/>
-      <c r="O70" s="3"/>
-      <c r="P70" s="3"/>
+      <c r="K70" t="s">
+        <v>190</v>
+      </c>
+      <c r="L70" t="s">
+        <v>191</v>
+      </c>
       <c r="Q70" s="3"/>
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
@@ -18506,9 +18535,12 @@
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
       <c r="J71" s="6"/>
-      <c r="N71" s="3"/>
-      <c r="O71" s="3"/>
-      <c r="P71" s="3"/>
+      <c r="K71" t="s">
+        <v>190</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="Q71" s="3"/>
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
@@ -18551,9 +18583,12 @@
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
       <c r="J72" s="6"/>
-      <c r="N72" s="3"/>
-      <c r="O72" s="3"/>
-      <c r="P72" s="3"/>
+      <c r="K72" t="s">
+        <v>190</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>193</v>
+      </c>
       <c r="Q72" s="3"/>
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
@@ -18596,10 +18631,12 @@
       <c r="H73" s="6"/>
       <c r="I73" s="6"/>
       <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
-      <c r="N73" s="3"/>
-      <c r="O73" s="3"/>
-      <c r="P73" s="3"/>
+      <c r="K73" t="s">
+        <v>190</v>
+      </c>
+      <c r="L73" s="6" t="s">
+        <v>194</v>
+      </c>
       <c r="Q73" s="3"/>
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
@@ -18643,9 +18680,6 @@
       <c r="I74" s="6"/>
       <c r="J74" s="6"/>
       <c r="K74" s="6"/>
-      <c r="N74" s="3"/>
-      <c r="O74" s="3"/>
-      <c r="P74" s="3"/>
       <c r="Q74" s="3"/>
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
@@ -18692,9 +18726,6 @@
       <c r="I75" s="6"/>
       <c r="J75" s="6"/>
       <c r="K75" s="6"/>
-      <c r="N75" s="3"/>
-      <c r="O75" s="3"/>
-      <c r="P75" s="3"/>
       <c r="Q75" s="3"/>
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
@@ -18741,9 +18772,6 @@
       <c r="I76" s="6"/>
       <c r="J76" s="6"/>
       <c r="K76" s="6"/>
-      <c r="N76" s="3"/>
-      <c r="O76" s="3"/>
-      <c r="P76" s="3"/>
       <c r="Q76" s="3"/>
       <c r="R76" s="3"/>
       <c r="S76" s="3"/>
@@ -18793,9 +18821,6 @@
       <c r="H77" s="6"/>
       <c r="I77" s="6"/>
       <c r="J77" s="6"/>
-      <c r="N77" s="3"/>
-      <c r="O77" s="3"/>
-      <c r="P77" s="3"/>
       <c r="Q77" s="3"/>
       <c r="R77" s="3"/>
       <c r="S77" s="3"/>
@@ -18843,9 +18868,6 @@
       <c r="H78" s="6"/>
       <c r="I78" s="6"/>
       <c r="J78" s="6"/>
-      <c r="N78" s="3"/>
-      <c r="O78" s="3"/>
-      <c r="P78" s="3"/>
       <c r="Q78" s="3"/>
       <c r="R78" s="3"/>
       <c r="S78" s="3"/>
@@ -18871,7 +18893,7 @@
         <v>87</v>
       </c>
       <c r="AC78" s="3" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="AD78" s="20"/>
       <c r="AE78" s="3"/>
@@ -18894,9 +18916,6 @@
       <c r="H79" s="6"/>
       <c r="I79" s="6"/>
       <c r="J79" s="6"/>
-      <c r="N79" s="3"/>
-      <c r="O79" s="3"/>
-      <c r="P79" s="3"/>
       <c r="Q79" s="3"/>
       <c r="R79" s="3"/>
       <c r="S79" s="3"/>
@@ -18931,8 +18950,6 @@
       <c r="H80" s="6"/>
       <c r="I80" s="6"/>
       <c r="J80" s="6"/>
-      <c r="N80" s="3"/>
-      <c r="O80" s="3"/>
       <c r="AA80" s="3"/>
       <c r="AB80" s="3"/>
       <c r="AC80" s="3"/>
@@ -19119,13 +19136,14 @@
       <c r="D86" s="12">
         <v>1</v>
       </c>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
-      <c r="G86" s="8"/>
+      <c r="E86" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="F86" s="25"/>
+      <c r="G86" s="25"/>
       <c r="H86" s="6"/>
       <c r="I86" s="6"/>
       <c r="J86" s="6"/>
-      <c r="M86" s="3"/>
       <c r="U86" s="3"/>
       <c r="V86" s="3"/>
       <c r="W86" s="3"/>
@@ -19150,10 +19168,22 @@
       <c r="G87" s="26">
         <v>0</v>
       </c>
-      <c r="H87" s="6"/>
+      <c r="H87" s="28" t="s">
+        <v>196</v>
+      </c>
       <c r="I87" s="6"/>
       <c r="J87" s="6"/>
-      <c r="M87" s="3"/>
+      <c r="K87" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="L87" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="N87" s="20"/>
+      <c r="O87" s="20"/>
+      <c r="P87" t="s">
+        <v>199</v>
+      </c>
       <c r="U87" s="3"/>
       <c r="V87" s="3"/>
       <c r="W87" s="3"/>
@@ -19179,10 +19209,20 @@
       <c r="G88" s="26">
         <v>1</v>
       </c>
-      <c r="H88" s="6"/>
+      <c r="H88" s="28" t="s">
+        <v>200</v>
+      </c>
       <c r="I88" s="6"/>
       <c r="J88" s="6"/>
-      <c r="M88" s="3"/>
+      <c r="K88" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="L88" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="M88" s="6"/>
+      <c r="N88" s="20"/>
+      <c r="O88" s="20"/>
       <c r="U88" s="3"/>
       <c r="V88" s="3"/>
       <c r="W88" s="3"/>
@@ -19211,7 +19251,10 @@
       <c r="H89" s="6"/>
       <c r="I89" s="6"/>
       <c r="J89" s="6"/>
-      <c r="M89" s="3"/>
+      <c r="K89" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="L89" s="6"/>
       <c r="U89" s="3"/>
       <c r="V89" s="3"/>
       <c r="W89" s="3"/>
@@ -19239,7 +19282,11 @@
       <c r="H90" s="6"/>
       <c r="I90" s="6"/>
       <c r="J90" s="6"/>
-      <c r="M90" s="3"/>
+      <c r="K90" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="L90" s="6"/>
+      <c r="M90" s="6"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
@@ -19267,7 +19314,11 @@
       <c r="H91" s="6"/>
       <c r="I91" s="6"/>
       <c r="J91" s="6"/>
-      <c r="M91" s="3"/>
+      <c r="K91" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="L91" s="6"/>
+      <c r="M91" s="6"/>
       <c r="U91" s="3"/>
       <c r="V91" s="3"/>
       <c r="W91" s="3"/>
@@ -19295,7 +19346,11 @@
       <c r="H92" s="6"/>
       <c r="I92" s="6"/>
       <c r="J92" s="6"/>
-      <c r="M92" s="3"/>
+      <c r="K92" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="L92" s="6"/>
+      <c r="M92" s="6"/>
       <c r="U92" s="3"/>
       <c r="V92" s="3"/>
       <c r="W92" s="3"/>
@@ -19323,7 +19378,11 @@
       <c r="H93" s="6"/>
       <c r="I93" s="6"/>
       <c r="J93" s="6"/>
-      <c r="M93" s="3"/>
+      <c r="K93" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="L93" s="6"/>
+      <c r="M93" s="6"/>
       <c r="U93" s="3"/>
       <c r="V93" s="3"/>
       <c r="W93" s="3"/>
@@ -19354,7 +19413,11 @@
       <c r="H94" s="6"/>
       <c r="I94" s="6"/>
       <c r="J94" s="6"/>
-      <c r="M94" s="3"/>
+      <c r="K94" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="L94" s="6"/>
+      <c r="M94" s="6"/>
       <c r="U94" s="3"/>
       <c r="V94" s="3"/>
       <c r="W94" s="3"/>
@@ -19387,6 +19450,7 @@
       <c r="H95" s="17"/>
       <c r="I95" s="17"/>
       <c r="J95" s="17"/>
+      <c r="K95" s="19"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
@@ -19424,6 +19488,7 @@
       <c r="H96" s="6"/>
       <c r="I96" s="6"/>
       <c r="J96" s="6"/>
+      <c r="K96" s="19"/>
       <c r="N96" s="3"/>
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
@@ -19461,6 +19526,7 @@
       <c r="H97" s="6"/>
       <c r="I97" s="6"/>
       <c r="J97" s="6"/>
+      <c r="K97" s="19"/>
       <c r="N97" s="3"/>
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
@@ -19498,6 +19564,7 @@
       <c r="H98" s="6"/>
       <c r="I98" s="6"/>
       <c r="J98" s="6"/>
+      <c r="K98" s="19"/>
       <c r="N98" s="3"/>
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
@@ -19522,6 +19589,7 @@
       <c r="H99" s="6"/>
       <c r="I99" s="6"/>
       <c r="J99" s="6"/>
+      <c r="K99" s="19"/>
       <c r="N99" s="3"/>
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
@@ -19546,6 +19614,7 @@
       <c r="H100" s="6"/>
       <c r="I100" s="6"/>
       <c r="J100" s="6"/>
+      <c r="K100" s="19"/>
       <c r="N100" s="3"/>
       <c r="O100" s="3"/>
       <c r="P100" s="3"/>
@@ -19570,6 +19639,7 @@
       <c r="H101" s="6"/>
       <c r="I101" s="6"/>
       <c r="J101" s="6"/>
+      <c r="K101" s="19"/>
       <c r="N101" s="3"/>
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
@@ -19594,6 +19664,7 @@
       <c r="H102" s="6"/>
       <c r="I102" s="6"/>
       <c r="J102" s="6"/>
+      <c r="K102" s="19"/>
       <c r="N102" s="3"/>
       <c r="O102" s="3"/>
       <c r="P102" s="3"/>
@@ -19625,6 +19696,7 @@
       <c r="H103" s="6"/>
       <c r="I103" s="6"/>
       <c r="J103" s="6"/>
+      <c r="K103" s="19"/>
       <c r="N103" s="3"/>
       <c r="O103" s="3"/>
       <c r="P103" s="3"/>
@@ -19654,6 +19726,7 @@
       <c r="H104" s="6"/>
       <c r="I104" s="6"/>
       <c r="J104" s="6"/>
+      <c r="K104" s="19"/>
       <c r="W104" s="6"/>
       <c r="X104" s="6"/>
       <c r="Y104" s="6"/>
@@ -19677,6 +19750,7 @@
       <c r="H105" s="6"/>
       <c r="I105" s="6"/>
       <c r="J105" s="6"/>
+      <c r="K105" s="19"/>
       <c r="W105" s="6"/>
       <c r="X105" s="6"/>
       <c r="Y105" s="6"/>
@@ -19700,6 +19774,7 @@
       <c r="H106" s="6"/>
       <c r="I106" s="6"/>
       <c r="J106" s="6"/>
+      <c r="K106" s="19"/>
       <c r="W106" s="6"/>
       <c r="X106" s="6"/>
       <c r="Y106" s="6"/>
@@ -19723,6 +19798,7 @@
       <c r="H107" s="6"/>
       <c r="I107" s="6"/>
       <c r="J107" s="6"/>
+      <c r="K107" s="19"/>
     </row>
     <row r="108" ht="14.25">
       <c r="A108" s="5"/>
@@ -19741,6 +19817,7 @@
       <c r="H108" s="6"/>
       <c r="I108" s="6"/>
       <c r="J108" s="6"/>
+      <c r="K108" s="19"/>
       <c r="N108" s="6"/>
       <c r="O108" s="6"/>
       <c r="P108" s="6"/>
@@ -19774,6 +19851,7 @@
       <c r="H109" s="6"/>
       <c r="I109" s="6"/>
       <c r="J109" s="6"/>
+      <c r="K109" s="19"/>
       <c r="N109" s="6"/>
       <c r="O109" s="6"/>
       <c r="P109" s="6"/>
@@ -19807,6 +19885,7 @@
       <c r="H110" s="6"/>
       <c r="I110" s="6"/>
       <c r="J110" s="6"/>
+      <c r="K110" s="19"/>
       <c r="N110" s="6"/>
       <c r="O110" s="6"/>
       <c r="P110" s="6"/>
@@ -19840,6 +19919,7 @@
       <c r="H111" s="6"/>
       <c r="I111" s="6"/>
       <c r="J111" s="6"/>
+      <c r="K111" s="19"/>
       <c r="N111" s="6"/>
       <c r="O111" s="6"/>
       <c r="P111" s="6"/>
@@ -19873,6 +19953,7 @@
       <c r="H112" s="6"/>
       <c r="I112" s="6"/>
       <c r="J112" s="6"/>
+      <c r="K112" s="19"/>
       <c r="N112" s="6"/>
       <c r="O112" s="6"/>
       <c r="P112" s="6"/>
@@ -19908,6 +19989,7 @@
       <c r="H113" s="6"/>
       <c r="I113" s="6"/>
       <c r="J113" s="6"/>
+      <c r="K113" s="19"/>
       <c r="N113" s="6"/>
       <c r="O113" s="6"/>
       <c r="P113" s="6"/>
@@ -19941,6 +20023,7 @@
       <c r="H114" s="6"/>
       <c r="I114" s="6"/>
       <c r="J114" s="6"/>
+      <c r="K114" s="19"/>
       <c r="N114" s="6"/>
       <c r="O114" s="6"/>
       <c r="P114" s="6"/>
@@ -19972,6 +20055,7 @@
       <c r="H115" s="6"/>
       <c r="I115" s="6"/>
       <c r="J115" s="6"/>
+      <c r="K115" s="19"/>
       <c r="N115" s="6"/>
       <c r="O115" s="6"/>
       <c r="P115" s="6"/>
@@ -20003,6 +20087,7 @@
       <c r="H116" s="6"/>
       <c r="I116" s="6"/>
       <c r="J116" s="6"/>
+      <c r="K116" s="19"/>
       <c r="N116" s="6"/>
       <c r="O116" s="6"/>
       <c r="P116" s="6"/>
@@ -20010,7 +20095,7 @@
       <c r="R116" s="6"/>
       <c r="X116" s="6"/>
       <c r="Z116" s="6"/>
-      <c r="AA116" s="27"/>
+      <c r="AA116" s="29"/>
       <c r="AH116" s="6"/>
       <c r="AI116" s="6"/>
       <c r="AJ116" s="6"/>
@@ -20037,6 +20122,7 @@
       <c r="H117" s="6"/>
       <c r="I117" s="6"/>
       <c r="J117" s="6"/>
+      <c r="K117" s="19"/>
       <c r="N117" s="6"/>
       <c r="O117" s="6"/>
       <c r="P117" s="6"/>
@@ -20068,6 +20154,7 @@
       <c r="H118" s="6"/>
       <c r="I118" s="6"/>
       <c r="J118" s="6"/>
+      <c r="K118" s="19"/>
       <c r="N118" s="6"/>
       <c r="O118" s="6"/>
       <c r="P118" s="6"/>
@@ -20099,6 +20186,7 @@
       <c r="H119" s="6"/>
       <c r="I119" s="6"/>
       <c r="J119" s="6"/>
+      <c r="K119" s="19"/>
       <c r="N119" s="6"/>
       <c r="O119" s="6"/>
       <c r="P119" s="6"/>
@@ -20130,6 +20218,7 @@
       <c r="H120" s="6"/>
       <c r="I120" s="6"/>
       <c r="J120" s="6"/>
+      <c r="K120" s="19"/>
       <c r="N120" s="6"/>
       <c r="O120" s="6"/>
       <c r="P120" s="6"/>
@@ -20161,6 +20250,7 @@
       <c r="H121" s="6"/>
       <c r="I121" s="6"/>
       <c r="J121" s="6"/>
+      <c r="K121" s="19"/>
       <c r="N121" s="6"/>
       <c r="O121" s="6"/>
       <c r="P121" s="6"/>
@@ -20194,6 +20284,7 @@
       <c r="H122" s="6"/>
       <c r="I122" s="6"/>
       <c r="J122" s="6"/>
+      <c r="K122" s="19"/>
       <c r="N122" s="6"/>
       <c r="O122" s="6"/>
       <c r="P122" s="6"/>
@@ -20225,6 +20316,7 @@
       <c r="H123" s="6"/>
       <c r="I123" s="6"/>
       <c r="J123" s="6"/>
+      <c r="K123" s="19"/>
       <c r="N123" s="6"/>
       <c r="O123" s="6"/>
       <c r="P123" s="6"/>
@@ -20256,6 +20348,7 @@
       <c r="H124" s="6"/>
       <c r="I124" s="6"/>
       <c r="J124" s="6"/>
+      <c r="K124" s="19"/>
       <c r="N124" s="6"/>
       <c r="O124" s="6"/>
       <c r="P124" s="6"/>
@@ -20287,6 +20380,7 @@
       <c r="H125" s="6"/>
       <c r="I125" s="6"/>
       <c r="J125" s="6"/>
+      <c r="K125" s="19"/>
       <c r="N125" s="6"/>
       <c r="O125" s="6"/>
       <c r="P125" s="6"/>
@@ -20318,6 +20412,7 @@
       <c r="H126" s="6"/>
       <c r="I126" s="6"/>
       <c r="J126" s="6"/>
+      <c r="K126" s="19"/>
     </row>
     <row r="127" ht="14.25">
       <c r="A127" s="5"/>
@@ -20336,6 +20431,7 @@
       <c r="H127" s="6"/>
       <c r="I127" s="6"/>
       <c r="J127" s="6"/>
+      <c r="K127" s="19"/>
     </row>
     <row r="128" ht="14.25">
       <c r="A128" s="5"/>
@@ -20354,6 +20450,7 @@
       <c r="H128" s="6"/>
       <c r="I128" s="6"/>
       <c r="J128" s="6"/>
+      <c r="K128" s="19"/>
     </row>
     <row r="129" ht="14.25">
       <c r="A129" s="5"/>
@@ -20372,6 +20469,7 @@
       <c r="H129" s="6"/>
       <c r="I129" s="6"/>
       <c r="J129" s="6"/>
+      <c r="K129" s="19"/>
     </row>
     <row r="130" ht="14.25">
       <c r="A130" s="5"/>
@@ -20390,6 +20488,7 @@
       <c r="H130" s="6"/>
       <c r="I130" s="6"/>
       <c r="J130" s="6"/>
+      <c r="K130" s="19"/>
     </row>
     <row r="131" ht="14.25">
       <c r="A131" s="12">
@@ -20410,6 +20509,7 @@
       <c r="H131" s="6"/>
       <c r="I131" s="6"/>
       <c r="J131" s="6"/>
+      <c r="K131" s="19"/>
     </row>
     <row r="132" ht="14.25">
       <c r="A132" s="5"/>
@@ -20428,12 +20528,7 @@
       <c r="H132" s="6"/>
       <c r="I132" s="6"/>
       <c r="J132" s="6"/>
-      <c r="K132" t="s">
-        <v>189</v>
-      </c>
-      <c r="L132" t="s">
-        <v>190</v>
-      </c>
+      <c r="K132" s="19"/>
     </row>
     <row r="133" ht="14.25">
       <c r="A133" s="5"/>
@@ -20452,12 +20547,7 @@
       <c r="H133" s="6"/>
       <c r="I133" s="6"/>
       <c r="J133" s="6"/>
-      <c r="K133" t="s">
-        <v>189</v>
-      </c>
-      <c r="L133" s="3" t="s">
-        <v>191</v>
-      </c>
+      <c r="K133" s="19"/>
     </row>
     <row r="134" ht="14.25">
       <c r="A134" s="5"/>
@@ -20476,12 +20566,7 @@
       <c r="H134" s="6"/>
       <c r="I134" s="6"/>
       <c r="J134" s="6"/>
-      <c r="K134" t="s">
-        <v>189</v>
-      </c>
-      <c r="L134" s="3" t="s">
-        <v>192</v>
-      </c>
+      <c r="K134" s="19"/>
     </row>
     <row r="135" ht="14.25">
       <c r="A135" s="5"/>
@@ -20500,12 +20585,7 @@
       <c r="H135" s="6"/>
       <c r="I135" s="6"/>
       <c r="J135" s="6"/>
-      <c r="K135" t="s">
-        <v>189</v>
-      </c>
-      <c r="L135" s="6" t="s">
-        <v>193</v>
-      </c>
+      <c r="K135" s="19"/>
     </row>
     <row r="136" ht="14.25">
       <c r="A136" s="5"/>
@@ -20524,6 +20604,7 @@
       <c r="H136" s="6"/>
       <c r="I136" s="6"/>
       <c r="J136" s="6"/>
+      <c r="K136" s="19"/>
     </row>
     <row r="137" ht="14.25">
       <c r="A137" s="5"/>
@@ -20542,6 +20623,7 @@
       <c r="H137" s="6"/>
       <c r="I137" s="6"/>
       <c r="J137" s="6"/>
+      <c r="K137" s="19"/>
     </row>
     <row r="138" ht="14.25">
       <c r="A138" s="5"/>
@@ -20560,6 +20642,7 @@
       <c r="H138" s="6"/>
       <c r="I138" s="6"/>
       <c r="J138" s="6"/>
+      <c r="K138" s="19"/>
     </row>
     <row r="139" ht="14.25">
       <c r="A139" s="5"/>
@@ -20578,6 +20661,7 @@
       <c r="H139" s="6"/>
       <c r="I139" s="6"/>
       <c r="J139" s="6"/>
+      <c r="K139" s="19"/>
     </row>
     <row r="140" ht="14.25">
       <c r="A140" s="12">
@@ -20598,6 +20682,7 @@
       <c r="H140" s="6"/>
       <c r="I140" s="6"/>
       <c r="J140" s="6"/>
+      <c r="K140" s="19"/>
     </row>
     <row r="141" ht="14.25">
       <c r="A141" s="5"/>
@@ -20616,6 +20701,7 @@
       <c r="H141" s="6"/>
       <c r="I141" s="6"/>
       <c r="J141" s="6"/>
+      <c r="K141" s="19"/>
     </row>
     <row r="142" ht="14.25">
       <c r="A142" s="5"/>
@@ -20634,6 +20720,7 @@
       <c r="H142" s="6"/>
       <c r="I142" s="6"/>
       <c r="J142" s="6"/>
+      <c r="K142" s="19"/>
     </row>
     <row r="143" ht="14.25">
       <c r="A143" s="5"/>
@@ -20652,6 +20739,7 @@
       <c r="H143" s="6"/>
       <c r="I143" s="6"/>
       <c r="J143" s="6"/>
+      <c r="K143" s="19"/>
     </row>
     <row r="144" ht="14.25">
       <c r="A144" s="5"/>
@@ -20670,6 +20758,7 @@
       <c r="H144" s="6"/>
       <c r="I144" s="6"/>
       <c r="J144" s="6"/>
+      <c r="K144" s="19"/>
     </row>
     <row r="145" ht="14.25">
       <c r="A145" s="5"/>
@@ -20688,6 +20777,7 @@
       <c r="H145" s="6"/>
       <c r="I145" s="6"/>
       <c r="J145" s="6"/>
+      <c r="K145" s="19"/>
     </row>
     <row r="146" ht="14.25">
       <c r="A146" s="5"/>
@@ -20706,6 +20796,7 @@
       <c r="H146" s="6"/>
       <c r="I146" s="6"/>
       <c r="J146" s="6"/>
+      <c r="K146" s="19"/>
     </row>
     <row r="147" ht="14.25">
       <c r="A147" s="5"/>
@@ -20724,6 +20815,7 @@
       <c r="H147" s="6"/>
       <c r="I147" s="6"/>
       <c r="J147" s="6"/>
+      <c r="K147" s="19"/>
     </row>
     <row r="148" ht="14.25">
       <c r="A148" s="5"/>
@@ -20742,6 +20834,7 @@
       <c r="H148" s="6"/>
       <c r="I148" s="6"/>
       <c r="J148" s="6"/>
+      <c r="K148" s="19"/>
     </row>
     <row r="149" ht="14.25">
       <c r="A149" s="12">
@@ -20762,6 +20855,7 @@
       <c r="H149" s="6"/>
       <c r="I149" s="6"/>
       <c r="J149" s="6"/>
+      <c r="K149" s="19"/>
     </row>
     <row r="150" ht="14.25">
       <c r="A150" s="5"/>
@@ -20780,6 +20874,7 @@
       <c r="H150" s="6"/>
       <c r="I150" s="6"/>
       <c r="J150" s="6"/>
+      <c r="K150" s="19"/>
     </row>
     <row r="151" ht="14.25">
       <c r="A151" s="5"/>
@@ -20798,6 +20893,7 @@
       <c r="H151" s="6"/>
       <c r="I151" s="6"/>
       <c r="J151" s="6"/>
+      <c r="K151" s="19"/>
     </row>
     <row r="152" ht="14.25">
       <c r="A152" s="5"/>
@@ -20816,6 +20912,7 @@
       <c r="H152" s="6"/>
       <c r="I152" s="6"/>
       <c r="J152" s="6"/>
+      <c r="K152" s="19"/>
     </row>
     <row r="153" ht="14.25">
       <c r="A153" s="5"/>
@@ -20834,6 +20931,7 @@
       <c r="H153" s="6"/>
       <c r="I153" s="6"/>
       <c r="J153" s="6"/>
+      <c r="K153" s="19"/>
     </row>
     <row r="154" ht="14.25">
       <c r="A154" s="5"/>
@@ -20852,7 +20950,7 @@
       <c r="H154" s="6"/>
       <c r="I154" s="6"/>
       <c r="J154" s="6"/>
-      <c r="K154" s="6"/>
+      <c r="K154" s="23"/>
       <c r="L154" s="6"/>
       <c r="M154" s="6"/>
     </row>
@@ -20873,7 +20971,7 @@
       <c r="H155" s="6"/>
       <c r="I155" s="6"/>
       <c r="J155" s="6"/>
-      <c r="K155" s="6"/>
+      <c r="K155" s="23"/>
       <c r="L155" s="6"/>
       <c r="M155" s="6"/>
     </row>
@@ -20894,7 +20992,7 @@
       <c r="H156" s="6"/>
       <c r="I156" s="6"/>
       <c r="J156" s="6"/>
-      <c r="K156" s="6"/>
+      <c r="K156" s="23"/>
     </row>
     <row r="157" ht="14.25">
       <c r="A157" s="5"/>
@@ -20913,6 +21011,7 @@
       <c r="H157" s="6"/>
       <c r="I157" s="6"/>
       <c r="J157" s="6"/>
+      <c r="K157" s="19"/>
     </row>
     <row r="158" ht="14.25">
       <c r="A158" s="12">
@@ -20927,15 +21026,13 @@
       <c r="D158" s="12">
         <v>1</v>
       </c>
-      <c r="E158" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="F158" s="25"/>
-      <c r="G158" s="25"/>
+      <c r="E158" s="8"/>
+      <c r="F158" s="8"/>
+      <c r="G158" s="8"/>
       <c r="H158" s="6"/>
       <c r="I158" s="6"/>
       <c r="J158" s="6"/>
-      <c r="K158" s="6"/>
+      <c r="K158" s="23"/>
       <c r="L158" s="6"/>
       <c r="M158" s="6"/>
     </row>
@@ -20956,18 +21053,7 @@
       <c r="H159" s="6"/>
       <c r="I159" s="6"/>
       <c r="J159" s="6"/>
-      <c r="K159" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="L159" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="M159" t="s">
-        <v>195</v>
-      </c>
-      <c r="N159" t="s">
-        <v>196</v>
-      </c>
+      <c r="K159" s="19"/>
       <c r="O159" s="6"/>
     </row>
     <row r="160" ht="14.25">
@@ -20987,18 +21073,7 @@
       <c r="H160" s="6"/>
       <c r="I160" s="6"/>
       <c r="J160" s="6"/>
-      <c r="K160" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="L160" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="M160" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="N160" s="6" t="s">
-        <v>196</v>
-      </c>
+      <c r="K160" s="19"/>
     </row>
     <row r="161" ht="14.25">
       <c r="A161" s="5"/>
@@ -21017,10 +21092,7 @@
       <c r="H161" s="6"/>
       <c r="I161" s="6"/>
       <c r="J161" s="6"/>
-      <c r="K161" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="L161" s="6"/>
+      <c r="K161" s="19"/>
       <c r="O161" s="6"/>
     </row>
     <row r="162" ht="14.25">
@@ -21040,11 +21112,7 @@
       <c r="H162" s="6"/>
       <c r="I162" s="6"/>
       <c r="J162" s="6"/>
-      <c r="K162" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="L162" s="6"/>
-      <c r="M162" s="6"/>
+      <c r="K162" s="19"/>
     </row>
     <row r="163" ht="14.25">
       <c r="A163" s="5"/>
@@ -21063,11 +21131,7 @@
       <c r="H163" s="6"/>
       <c r="I163" s="6"/>
       <c r="J163" s="6"/>
-      <c r="K163" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="L163" s="6"/>
-      <c r="M163" s="6"/>
+      <c r="K163" s="19"/>
     </row>
     <row r="164" ht="14.25">
       <c r="A164" s="5"/>
@@ -21086,11 +21150,7 @@
       <c r="H164" s="6"/>
       <c r="I164" s="6"/>
       <c r="J164" s="6"/>
-      <c r="K164" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="L164" s="6"/>
-      <c r="M164" s="6"/>
+      <c r="K164" s="19"/>
       <c r="O164" s="6"/>
     </row>
     <row r="165" ht="14.25">
@@ -21110,11 +21170,7 @@
       <c r="H165" s="6"/>
       <c r="I165" s="6"/>
       <c r="J165" s="6"/>
-      <c r="K165" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="L165" s="6"/>
-      <c r="M165" s="6"/>
+      <c r="K165" s="19"/>
       <c r="O165" s="6"/>
     </row>
     <row r="166" ht="14.25">
@@ -21134,11 +21190,7 @@
       <c r="H166" s="6"/>
       <c r="I166" s="6"/>
       <c r="J166" s="6"/>
-      <c r="K166" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="L166" s="6"/>
-      <c r="M166" s="6"/>
+      <c r="K166" s="19"/>
       <c r="O166" s="6"/>
     </row>
     <row r="167" ht="14.25">
@@ -27233,7 +27285,7 @@
     </row>
     <row r="4" ht="14.25">
       <c r="A4" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -27448,52 +27500,52 @@
       <c r="P7" s="9">
         <v>1</v>
       </c>
-      <c r="Q7" s="28">
-        <v>0</v>
-      </c>
-      <c r="R7" s="28">
-        <v>0</v>
-      </c>
-      <c r="S7" s="28">
-        <v>0</v>
-      </c>
-      <c r="T7" s="28">
-        <v>0</v>
-      </c>
-      <c r="U7" s="28">
-        <v>0</v>
-      </c>
-      <c r="V7" s="28">
-        <v>0</v>
-      </c>
-      <c r="W7" s="28">
-        <v>0</v>
-      </c>
-      <c r="X7" s="28">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="28">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="28">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="28">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="28">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="28">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="28">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="28">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="28">
+      <c r="Q7" s="31">
+        <v>0</v>
+      </c>
+      <c r="R7" s="31">
+        <v>0</v>
+      </c>
+      <c r="S7" s="31">
+        <v>0</v>
+      </c>
+      <c r="T7" s="31">
+        <v>0</v>
+      </c>
+      <c r="U7" s="31">
+        <v>0</v>
+      </c>
+      <c r="V7" s="31">
+        <v>0</v>
+      </c>
+      <c r="W7" s="31">
+        <v>0</v>
+      </c>
+      <c r="X7" s="31">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="31">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="31">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="31">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="31">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="31">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="31">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="31">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="31">
         <v>1</v>
       </c>
       <c r="AG7" t="s">
@@ -27503,7 +27555,7 @@
         <v>40</v>
       </c>
       <c r="AI7" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AL7" t="str">
         <f t="shared" ref="AL7:AL9" si="0">BIN2HEX(_xlfn.CONCAT(A7:H7),2)</f>
@@ -27571,62 +27623,62 @@
       <c r="P8" s="9">
         <v>0</v>
       </c>
-      <c r="Q8" s="28">
-        <v>1</v>
-      </c>
-      <c r="R8" s="28">
-        <v>0</v>
-      </c>
-      <c r="S8" s="28">
-        <v>1</v>
-      </c>
-      <c r="T8" s="28">
-        <v>0</v>
-      </c>
-      <c r="U8" s="28">
-        <v>1</v>
-      </c>
-      <c r="V8" s="28">
-        <v>0</v>
-      </c>
-      <c r="W8" s="28">
-        <v>1</v>
-      </c>
-      <c r="X8" s="28">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="28">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="28">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="28">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="28">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="28">
-        <v>1</v>
-      </c>
-      <c r="AD8" s="28">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="28">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="28">
+      <c r="Q8" s="31">
+        <v>1</v>
+      </c>
+      <c r="R8" s="31">
+        <v>0</v>
+      </c>
+      <c r="S8" s="31">
+        <v>1</v>
+      </c>
+      <c r="T8" s="31">
+        <v>0</v>
+      </c>
+      <c r="U8" s="31">
+        <v>1</v>
+      </c>
+      <c r="V8" s="31">
+        <v>0</v>
+      </c>
+      <c r="W8" s="31">
+        <v>1</v>
+      </c>
+      <c r="X8" s="31">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="31">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="31">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="31">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="31">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="31">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="31">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="31">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="31">
         <v>1</v>
       </c>
       <c r="AG8" t="s">
         <v>44</v>
       </c>
       <c r="AH8" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AI8" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="AL8" s="6" t="str">
         <f t="shared" si="0"/>
@@ -27694,62 +27746,62 @@
       <c r="P9" s="9">
         <v>0</v>
       </c>
-      <c r="Q9" s="28">
-        <v>1</v>
-      </c>
-      <c r="R9" s="28">
-        <v>1</v>
-      </c>
-      <c r="S9" s="28">
-        <v>0</v>
-      </c>
-      <c r="T9" s="28">
-        <v>1</v>
-      </c>
-      <c r="U9" s="28">
-        <v>1</v>
-      </c>
-      <c r="V9" s="28">
-        <v>1</v>
-      </c>
-      <c r="W9" s="28">
-        <v>1</v>
-      </c>
-      <c r="X9" s="28">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="28">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="28">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="28">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="28">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="28">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="28">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="28">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="28">
+      <c r="Q9" s="31">
+        <v>1</v>
+      </c>
+      <c r="R9" s="31">
+        <v>1</v>
+      </c>
+      <c r="S9" s="31">
+        <v>0</v>
+      </c>
+      <c r="T9" s="31">
+        <v>1</v>
+      </c>
+      <c r="U9" s="31">
+        <v>1</v>
+      </c>
+      <c r="V9" s="31">
+        <v>1</v>
+      </c>
+      <c r="W9" s="31">
+        <v>1</v>
+      </c>
+      <c r="X9" s="31">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="31">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="31">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="31">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="31">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="31">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="31">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="31">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="31">
         <v>0</v>
       </c>
       <c r="AG9" t="s">
         <v>35</v>
       </c>
       <c r="AH9" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AI9" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AL9" s="6" t="str">
         <f t="shared" si="0"/>
@@ -27869,13 +27921,13 @@
         <v>131</v>
       </c>
       <c r="AH10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AI10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AJ10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AL10" s="6" t="str">
         <f t="shared" ref="AL10:AL18" si="4">BIN2HEX(_xlfn.CONCAT(A10:H10),2)</f>
@@ -27995,10 +28047,10 @@
         <v>131</v>
       </c>
       <c r="AH11" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AI11" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AJ11" t="s">
         <v>40</v>
@@ -28164,10 +28216,10 @@
         <v>131</v>
       </c>
       <c r="AH12" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AI12" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AJ12" t="s">
         <v>40</v>
@@ -28333,10 +28385,10 @@
         <v>131</v>
       </c>
       <c r="AH13" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AI13" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AJ13" t="s">
         <v>40</v>
@@ -28502,10 +28554,10 @@
         <v>131</v>
       </c>
       <c r="AH14" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AI14" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AJ14" t="s">
         <v>40</v>
@@ -28671,16 +28723,16 @@
         <v>131</v>
       </c>
       <c r="AH15" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AI15" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AJ15" s="6" t="s">
         <v>40</v>
       </c>
       <c r="AK15" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AL15" s="6" t="str">
         <f t="shared" si="4"/>
@@ -28843,16 +28895,16 @@
         <v>131</v>
       </c>
       <c r="AH16" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AI16" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AJ16" s="6" t="s">
         <v>40</v>
       </c>
       <c r="AK16" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AL16" s="6" t="str">
         <f t="shared" si="4"/>
@@ -29015,16 +29067,16 @@
         <v>131</v>
       </c>
       <c r="AH17" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AI17" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AJ17" s="6" t="s">
         <v>40</v>
       </c>
       <c r="AK17" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AL17" s="6" t="str">
         <f t="shared" si="4"/>
@@ -29120,49 +29172,49 @@
       <c r="K18" s="19">
         <v>0</v>
       </c>
-      <c r="L18" s="28">
-        <v>0</v>
-      </c>
-      <c r="M18" s="28">
-        <v>0</v>
-      </c>
-      <c r="N18" s="28">
-        <v>0</v>
-      </c>
-      <c r="O18" s="28">
-        <v>0</v>
-      </c>
-      <c r="P18" s="28">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="28">
-        <v>0</v>
-      </c>
-      <c r="R18" s="28">
-        <v>0</v>
-      </c>
-      <c r="S18" s="28">
-        <v>0</v>
-      </c>
-      <c r="T18" s="28">
-        <v>0</v>
-      </c>
-      <c r="U18" s="28">
-        <v>0</v>
-      </c>
-      <c r="V18" s="28">
-        <v>0</v>
-      </c>
-      <c r="W18" s="28">
-        <v>0</v>
-      </c>
-      <c r="X18" s="28">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="28">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="28">
+      <c r="L18" s="31">
+        <v>0</v>
+      </c>
+      <c r="M18" s="31">
+        <v>0</v>
+      </c>
+      <c r="N18" s="31">
+        <v>0</v>
+      </c>
+      <c r="O18" s="31">
+        <v>0</v>
+      </c>
+      <c r="P18" s="31">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="31">
+        <v>0</v>
+      </c>
+      <c r="R18" s="31">
+        <v>0</v>
+      </c>
+      <c r="S18" s="31">
+        <v>0</v>
+      </c>
+      <c r="T18" s="31">
+        <v>0</v>
+      </c>
+      <c r="U18" s="31">
+        <v>0</v>
+      </c>
+      <c r="V18" s="31">
+        <v>0</v>
+      </c>
+      <c r="W18" s="31">
+        <v>0</v>
+      </c>
+      <c r="X18" s="31">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="31">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="31">
         <v>0</v>
       </c>
       <c r="AA18" s="13">
@@ -29392,7 +29444,7 @@
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -44286,7 +44338,7 @@
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
       <c r="AA13" s="8" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AB13" s="8"/>
       <c r="AC13" s="8"/>
@@ -44402,7 +44454,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -44586,13 +44638,13 @@
       <c r="AS19" t="s">
         <v>26</v>
       </c>
-      <c r="AX19" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AY19" s="29"/>
-      <c r="AZ19" s="29"/>
-      <c r="BA19" s="29"/>
-      <c r="BB19" s="29"/>
+      <c r="AX19" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AY19" s="32"/>
+      <c r="AZ19" s="32"/>
+      <c r="BA19" s="32"/>
+      <c r="BB19" s="32"/>
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="5"/>
@@ -44722,17 +44774,17 @@
       <c r="AX21" s="6">
         <v>0</v>
       </c>
-      <c r="AY21" s="27">
+      <c r="AY21" s="29">
         <v>0</v>
       </c>
       <c r="AZ21" t="s">
         <v>135</v>
       </c>
-      <c r="BA21" s="30" t="s">
-        <v>211</v>
+      <c r="BA21" s="33" t="s">
+        <v>215</v>
       </c>
       <c r="BB21" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" ht="14.25">
@@ -44798,13 +44850,13 @@
       <c r="AX22" s="6">
         <v>0</v>
       </c>
-      <c r="AY22" s="27">
+      <c r="AY22" s="29">
         <v>1</v>
       </c>
       <c r="AZ22" t="s">
-        <v>213</v>
-      </c>
-      <c r="BA22" s="30"/>
+        <v>217</v>
+      </c>
+      <c r="BA22" s="33"/>
     </row>
     <row r="23" ht="14.25">
       <c r="A23" s="5"/>
@@ -44815,7 +44867,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
@@ -44867,13 +44919,13 @@
       <c r="AX23" s="6">
         <v>0</v>
       </c>
-      <c r="AY23" s="27">
+      <c r="AY23" s="29">
         <v>2</v>
       </c>
       <c r="AZ23" t="s">
-        <v>215</v>
-      </c>
-      <c r="BA23" s="30"/>
+        <v>219</v>
+      </c>
+      <c r="BA23" s="33"/>
     </row>
     <row r="24" ht="14.25">
       <c r="A24" s="5"/>
@@ -44940,13 +44992,13 @@
       <c r="AX24" s="6">
         <v>0</v>
       </c>
-      <c r="AY24" s="27">
+      <c r="AY24" s="29">
         <v>3</v>
       </c>
       <c r="AZ24" t="s">
-        <v>216</v>
-      </c>
-      <c r="BA24" s="30"/>
+        <v>220</v>
+      </c>
+      <c r="BA24" s="33"/>
       <c r="BW24" s="6"/>
       <c r="BX24" s="6"/>
       <c r="BY24" s="6"/>
@@ -44971,7 +45023,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
@@ -45020,7 +45072,7 @@
       <c r="AX25" s="6">
         <v>0</v>
       </c>
-      <c r="AY25" s="27">
+      <c r="AY25" s="29">
         <v>4</v>
       </c>
       <c r="AZ25" t="s">
@@ -45054,7 +45106,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
@@ -45101,7 +45153,7 @@
       <c r="AX26" s="6">
         <v>0</v>
       </c>
-      <c r="AY26" s="27">
+      <c r="AY26" s="29">
         <v>5</v>
       </c>
       <c r="AZ26" t="s">
@@ -45180,7 +45232,7 @@
       <c r="AX27" s="6">
         <v>0</v>
       </c>
-      <c r="AY27" s="27">
+      <c r="AY27" s="29">
         <v>6</v>
       </c>
       <c r="AZ27" t="s">
@@ -45212,7 +45264,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
@@ -45261,7 +45313,7 @@
       <c r="AX28" s="6">
         <v>0</v>
       </c>
-      <c r="AY28" s="27">
+      <c r="AY28" s="29">
         <v>7</v>
       </c>
       <c r="AZ28" t="s">
@@ -45293,7 +45345,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
@@ -45342,24 +45394,24 @@
       <c r="AX29" s="6">
         <v>0</v>
       </c>
-      <c r="AY29" s="27">
+      <c r="AY29" s="29">
         <v>8</v>
       </c>
       <c r="AZ29" t="s">
         <v>147</v>
       </c>
       <c r="BL29" s="14" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="BM29" s="14"/>
       <c r="BN29" s="14"/>
-      <c r="BO29" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="BP29" s="29"/>
-      <c r="BQ29" s="29"/>
-      <c r="BR29" s="29"/>
-      <c r="BS29" s="29"/>
+      <c r="BO29" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="BP29" s="32"/>
+      <c r="BQ29" s="32"/>
+      <c r="BR29" s="32"/>
+      <c r="BS29" s="32"/>
     </row>
     <row r="30" ht="14.25">
       <c r="A30" s="5"/>
@@ -45377,7 +45429,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
@@ -45424,14 +45476,14 @@
       <c r="AX30" s="6">
         <v>0</v>
       </c>
-      <c r="AY30" s="27">
+      <c r="AY30" s="29">
         <v>9</v>
       </c>
       <c r="AZ30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BK30" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="BL30" s="6">
         <v>0</v>
@@ -45464,7 +45516,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
@@ -45513,14 +45565,14 @@
       <c r="AX31" s="6">
         <v>0</v>
       </c>
-      <c r="AY31" s="27" t="s">
-        <v>219</v>
+      <c r="AY31" s="29" t="s">
+        <v>223</v>
       </c>
       <c r="AZ31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BK31" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="BL31" s="6">
         <v>0</v>
@@ -45658,14 +45710,14 @@
       <c r="AX32" s="6">
         <v>0</v>
       </c>
-      <c r="AY32" s="27" t="s">
-        <v>221</v>
+      <c r="AY32" s="29" t="s">
+        <v>225</v>
       </c>
       <c r="AZ32" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="BK32" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="BL32" s="6">
         <v>0</v>
@@ -45749,14 +45801,14 @@
       <c r="AX33" s="6">
         <v>0</v>
       </c>
-      <c r="AY33" s="27" t="s">
-        <v>223</v>
+      <c r="AY33" s="29" t="s">
+        <v>227</v>
       </c>
       <c r="AZ33" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="BK33" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="BL33" s="6">
         <v>0</v>
@@ -45846,14 +45898,14 @@
       <c r="AX34" s="6">
         <v>0</v>
       </c>
-      <c r="AY34" s="27" t="s">
-        <v>225</v>
+      <c r="AY34" s="29" t="s">
+        <v>229</v>
       </c>
       <c r="AZ34" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="BK34" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="BL34" s="6">
         <v>1</v>
@@ -45927,11 +45979,11 @@
       <c r="AX35" s="6">
         <v>0</v>
       </c>
-      <c r="AY35" s="27" t="s">
-        <v>227</v>
+      <c r="AY35" s="29" t="s">
+        <v>231</v>
       </c>
       <c r="BK35" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="BL35" s="6">
         <v>1</v>
@@ -45955,7 +46007,7 @@
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="7" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
@@ -46005,8 +46057,8 @@
       <c r="AX36" s="6">
         <v>0</v>
       </c>
-      <c r="AY36" s="27" t="s">
-        <v>230</v>
+      <c r="AY36" s="29" t="s">
+        <v>234</v>
       </c>
       <c r="BL36" s="6">
         <v>1</v>
@@ -46039,7 +46091,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
@@ -46083,7 +46135,7 @@
       <c r="AX37" s="6">
         <v>1</v>
       </c>
-      <c r="AY37" s="27">
+      <c r="AY37" s="29">
         <v>0</v>
       </c>
       <c r="BL37" s="6">
@@ -46117,7 +46169,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
@@ -46161,7 +46213,7 @@
       <c r="AX38" s="6">
         <v>1</v>
       </c>
-      <c r="AY38" s="27">
+      <c r="AY38" s="29">
         <v>1</v>
       </c>
     </row>
@@ -46181,7 +46233,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
@@ -46225,12 +46277,12 @@
         <v>136</v>
       </c>
       <c r="AS39" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AX39" s="6">
         <v>1</v>
       </c>
-      <c r="AY39" s="27">
+      <c r="AY39" s="29">
         <v>2</v>
       </c>
     </row>
@@ -46250,7 +46302,7 @@
         <v>1</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
@@ -46296,7 +46348,7 @@
       <c r="AX40" s="6">
         <v>1</v>
       </c>
-      <c r="AY40" s="27">
+      <c r="AY40" s="29">
         <v>3</v>
       </c>
     </row>
@@ -46316,7 +46368,7 @@
         <v>0</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
@@ -46359,7 +46411,7 @@
       <c r="AX41" s="6">
         <v>1</v>
       </c>
-      <c r="AY41" s="27">
+      <c r="AY41" s="29">
         <v>4</v>
       </c>
     </row>
@@ -46379,7 +46431,7 @@
         <v>1</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -46422,7 +46474,7 @@
       <c r="AX42" s="6">
         <v>1</v>
       </c>
-      <c r="AY42" s="27">
+      <c r="AY42" s="29">
         <v>5</v>
       </c>
     </row>
@@ -46442,7 +46494,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
@@ -46483,12 +46535,12 @@
         <v>0</v>
       </c>
       <c r="AR43" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AX43" s="6">
         <v>1</v>
       </c>
-      <c r="AY43" s="27">
+      <c r="AY43" s="29">
         <v>6</v>
       </c>
     </row>
@@ -46508,7 +46560,7 @@
         <v>1</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
@@ -46551,7 +46603,7 @@
       <c r="AX44" s="6">
         <v>1</v>
       </c>
-      <c r="AY44" s="27">
+      <c r="AY44" s="29">
         <v>7</v>
       </c>
     </row>
@@ -46670,7 +46722,7 @@
       <c r="AX45" s="6">
         <v>1</v>
       </c>
-      <c r="AY45" s="27">
+      <c r="AY45" s="29">
         <v>8</v>
       </c>
     </row>
@@ -46739,7 +46791,7 @@
       <c r="AX46" s="6">
         <v>1</v>
       </c>
-      <c r="AY46" s="27">
+      <c r="AY46" s="29">
         <v>9</v>
       </c>
     </row>
@@ -46812,8 +46864,8 @@
       <c r="AX47" s="6">
         <v>1</v>
       </c>
-      <c r="AY47" s="27" t="s">
-        <v>219</v>
+      <c r="AY47" s="29" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="48" ht="14.25">
@@ -46869,8 +46921,8 @@
       <c r="AX48" s="6">
         <v>1</v>
       </c>
-      <c r="AY48" s="27" t="s">
-        <v>221</v>
+      <c r="AY48" s="29" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="49" ht="14.25">
@@ -46988,8 +47040,8 @@
       <c r="AX49" s="6">
         <v>1</v>
       </c>
-      <c r="AY49" s="27" t="s">
-        <v>223</v>
+      <c r="AY49" s="29" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="50" ht="14.25">
@@ -47053,8 +47105,8 @@
       <c r="AX50" s="6">
         <v>1</v>
       </c>
-      <c r="AY50" s="27" t="s">
-        <v>225</v>
+      <c r="AY50" s="29" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="51" ht="14.25">
@@ -47111,8 +47163,8 @@
       <c r="AX51" s="6">
         <v>1</v>
       </c>
-      <c r="AY51" s="27" t="s">
-        <v>227</v>
+      <c r="AY51" s="29" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="52" ht="14.25">
@@ -47215,83 +47267,83 @@
       <c r="AX52" s="6">
         <v>1</v>
       </c>
-      <c r="AY52" s="27" t="s">
-        <v>230</v>
+      <c r="AY52" s="29" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="53" ht="14.25">
-      <c r="A53" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
+      <c r="A53" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="B53" s="34"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="A54" s="31"/>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
+      <c r="A54" s="34"/>
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="34"/>
     </row>
     <row r="55" ht="14.25">
-      <c r="A55" s="31"/>
-      <c r="B55" s="31"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31"/>
+      <c r="A55" s="34"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
       <c r="AE55" s="5"/>
       <c r="AF55" s="5"/>
     </row>
     <row r="56" ht="14.25">
-      <c r="A56" s="31"/>
-      <c r="B56" s="31"/>
-      <c r="C56" s="31"/>
-      <c r="D56" s="31"/>
-      <c r="E56" s="31"/>
+      <c r="A56" s="34"/>
+      <c r="B56" s="34"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="34"/>
     </row>
     <row r="57" ht="14.25">
-      <c r="A57" s="31"/>
-      <c r="B57" s="31"/>
-      <c r="C57" s="31"/>
-      <c r="D57" s="31"/>
-      <c r="E57" s="31"/>
+      <c r="A57" s="34"/>
+      <c r="B57" s="34"/>
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="34"/>
     </row>
     <row r="58" ht="14.25">
-      <c r="A58" s="31"/>
-      <c r="B58" s="31"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31"/>
+      <c r="A58" s="34"/>
+      <c r="B58" s="34"/>
+      <c r="C58" s="34"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="34"/>
     </row>
     <row r="59" ht="14.25">
-      <c r="A59" s="31"/>
-      <c r="B59" s="31"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31"/>
+      <c r="A59" s="34"/>
+      <c r="B59" s="34"/>
+      <c r="C59" s="34"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="34"/>
     </row>
     <row r="60" ht="14.25">
-      <c r="A60" s="31"/>
-      <c r="B60" s="31"/>
-      <c r="C60" s="31"/>
-      <c r="D60" s="31"/>
-      <c r="E60" s="31"/>
+      <c r="A60" s="34"/>
+      <c r="B60" s="34"/>
+      <c r="C60" s="34"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="34"/>
     </row>
     <row r="61" ht="14.25">
-      <c r="A61" s="31"/>
-      <c r="B61" s="31"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31"/>
+      <c r="A61" s="34"/>
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="34"/>
     </row>
     <row r="62" ht="14.25">
-      <c r="A62" s="31"/>
-      <c r="B62" s="31"/>
-      <c r="C62" s="31"/>
-      <c r="D62" s="31"/>
-      <c r="E62" s="31"/>
+      <c r="A62" s="34"/>
+      <c r="B62" s="34"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="34"/>
     </row>
     <row r="67" ht="14.25">
       <c r="A67" s="6">
@@ -47773,7 +47825,7 @@
     </row>
     <row r="76" ht="14.25">
       <c r="A76" s="7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
@@ -47861,7 +47913,7 @@
     </row>
     <row r="78" ht="14.25">
       <c r="AA78" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="89" ht="14.25">
@@ -47964,7 +48016,7 @@
     </row>
     <row r="90" ht="14.25">
       <c r="A90" s="7" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
@@ -48052,7 +48104,7 @@
     </row>
     <row r="92" ht="14.25">
       <c r="AA92" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="100" ht="14.25">
@@ -48369,52 +48421,52 @@
       <c r="P111" s="9">
         <v>1</v>
       </c>
-      <c r="Q111" s="28">
-        <v>0</v>
-      </c>
-      <c r="R111" s="28">
-        <v>0</v>
-      </c>
-      <c r="S111" s="28">
-        <v>0</v>
-      </c>
-      <c r="T111" s="28">
-        <v>0</v>
-      </c>
-      <c r="U111" s="28">
-        <v>0</v>
-      </c>
-      <c r="V111" s="28">
-        <v>0</v>
-      </c>
-      <c r="W111" s="28">
-        <v>0</v>
-      </c>
-      <c r="X111" s="28">
-        <v>0</v>
-      </c>
-      <c r="Y111" s="28">
-        <v>0</v>
-      </c>
-      <c r="Z111" s="28">
-        <v>0</v>
-      </c>
-      <c r="AA111" s="28">
-        <v>0</v>
-      </c>
-      <c r="AB111" s="28">
-        <v>0</v>
-      </c>
-      <c r="AC111" s="28">
-        <v>0</v>
-      </c>
-      <c r="AD111" s="28">
-        <v>0</v>
-      </c>
-      <c r="AE111" s="28">
-        <v>0</v>
-      </c>
-      <c r="AF111" s="28">
+      <c r="Q111" s="31">
+        <v>0</v>
+      </c>
+      <c r="R111" s="31">
+        <v>0</v>
+      </c>
+      <c r="S111" s="31">
+        <v>0</v>
+      </c>
+      <c r="T111" s="31">
+        <v>0</v>
+      </c>
+      <c r="U111" s="31">
+        <v>0</v>
+      </c>
+      <c r="V111" s="31">
+        <v>0</v>
+      </c>
+      <c r="W111" s="31">
+        <v>0</v>
+      </c>
+      <c r="X111" s="31">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="31">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="31">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="31">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="31">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="31">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="31">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="31">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="31">
         <v>1</v>
       </c>
       <c r="AG111" t="s">
@@ -48424,7 +48476,7 @@
         <v>40</v>
       </c>
       <c r="AI111" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AL111" t="str">
         <f t="shared" ref="AL111:AL121" si="8">BIN2HEX(_xlfn.CONCAT(A111:H111),2)</f>
@@ -48492,62 +48544,62 @@
       <c r="P112" s="9">
         <v>0</v>
       </c>
-      <c r="Q112" s="28">
-        <v>1</v>
-      </c>
-      <c r="R112" s="28">
-        <v>0</v>
-      </c>
-      <c r="S112" s="28">
-        <v>1</v>
-      </c>
-      <c r="T112" s="28">
-        <v>0</v>
-      </c>
-      <c r="U112" s="28">
-        <v>1</v>
-      </c>
-      <c r="V112" s="28">
-        <v>0</v>
-      </c>
-      <c r="W112" s="28">
-        <v>1</v>
-      </c>
-      <c r="X112" s="28">
-        <v>1</v>
-      </c>
-      <c r="Y112" s="28">
-        <v>1</v>
-      </c>
-      <c r="Z112" s="28">
-        <v>1</v>
-      </c>
-      <c r="AA112" s="28">
-        <v>0</v>
-      </c>
-      <c r="AB112" s="28">
-        <v>0</v>
-      </c>
-      <c r="AC112" s="28">
-        <v>1</v>
-      </c>
-      <c r="AD112" s="28">
-        <v>1</v>
-      </c>
-      <c r="AE112" s="28">
-        <v>0</v>
-      </c>
-      <c r="AF112" s="28">
+      <c r="Q112" s="31">
+        <v>1</v>
+      </c>
+      <c r="R112" s="31">
+        <v>0</v>
+      </c>
+      <c r="S112" s="31">
+        <v>1</v>
+      </c>
+      <c r="T112" s="31">
+        <v>0</v>
+      </c>
+      <c r="U112" s="31">
+        <v>1</v>
+      </c>
+      <c r="V112" s="31">
+        <v>0</v>
+      </c>
+      <c r="W112" s="31">
+        <v>1</v>
+      </c>
+      <c r="X112" s="31">
+        <v>1</v>
+      </c>
+      <c r="Y112" s="31">
+        <v>1</v>
+      </c>
+      <c r="Z112" s="31">
+        <v>1</v>
+      </c>
+      <c r="AA112" s="31">
+        <v>0</v>
+      </c>
+      <c r="AB112" s="31">
+        <v>0</v>
+      </c>
+      <c r="AC112" s="31">
+        <v>1</v>
+      </c>
+      <c r="AD112" s="31">
+        <v>1</v>
+      </c>
+      <c r="AE112" s="31">
+        <v>0</v>
+      </c>
+      <c r="AF112" s="31">
         <v>1</v>
       </c>
       <c r="AG112" t="s">
         <v>44</v>
       </c>
       <c r="AH112" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AI112" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="AL112" s="6" t="str">
         <f t="shared" si="8"/>
@@ -48615,62 +48667,62 @@
       <c r="P113" s="9">
         <v>0</v>
       </c>
-      <c r="Q113" s="28">
-        <v>1</v>
-      </c>
-      <c r="R113" s="28">
-        <v>1</v>
-      </c>
-      <c r="S113" s="28">
-        <v>0</v>
-      </c>
-      <c r="T113" s="28">
-        <v>1</v>
-      </c>
-      <c r="U113" s="28">
-        <v>1</v>
-      </c>
-      <c r="V113" s="28">
-        <v>1</v>
-      </c>
-      <c r="W113" s="28">
-        <v>1</v>
-      </c>
-      <c r="X113" s="28">
-        <v>1</v>
-      </c>
-      <c r="Y113" s="28">
-        <v>1</v>
-      </c>
-      <c r="Z113" s="28">
-        <v>1</v>
-      </c>
-      <c r="AA113" s="28">
-        <v>1</v>
-      </c>
-      <c r="AB113" s="28">
-        <v>0</v>
-      </c>
-      <c r="AC113" s="28">
-        <v>0</v>
-      </c>
-      <c r="AD113" s="28">
-        <v>0</v>
-      </c>
-      <c r="AE113" s="28">
-        <v>0</v>
-      </c>
-      <c r="AF113" s="28">
+      <c r="Q113" s="31">
+        <v>1</v>
+      </c>
+      <c r="R113" s="31">
+        <v>1</v>
+      </c>
+      <c r="S113" s="31">
+        <v>0</v>
+      </c>
+      <c r="T113" s="31">
+        <v>1</v>
+      </c>
+      <c r="U113" s="31">
+        <v>1</v>
+      </c>
+      <c r="V113" s="31">
+        <v>1</v>
+      </c>
+      <c r="W113" s="31">
+        <v>1</v>
+      </c>
+      <c r="X113" s="31">
+        <v>1</v>
+      </c>
+      <c r="Y113" s="31">
+        <v>1</v>
+      </c>
+      <c r="Z113" s="31">
+        <v>1</v>
+      </c>
+      <c r="AA113" s="31">
+        <v>1</v>
+      </c>
+      <c r="AB113" s="31">
+        <v>0</v>
+      </c>
+      <c r="AC113" s="31">
+        <v>0</v>
+      </c>
+      <c r="AD113" s="31">
+        <v>0</v>
+      </c>
+      <c r="AE113" s="31">
+        <v>0</v>
+      </c>
+      <c r="AF113" s="31">
         <v>0</v>
       </c>
       <c r="AG113" t="s">
         <v>35</v>
       </c>
       <c r="AH113" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AI113" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AL113" s="6" t="str">
         <f t="shared" si="8"/>
@@ -48790,13 +48842,13 @@
         <v>131</v>
       </c>
       <c r="AH114" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AI114" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AJ114" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AL114" s="6" t="str">
         <f t="shared" si="8"/>
@@ -48916,10 +48968,10 @@
         <v>131</v>
       </c>
       <c r="AH115" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AI115" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AJ115" t="s">
         <v>40</v>
@@ -49042,10 +49094,10 @@
         <v>131</v>
       </c>
       <c r="AH116" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AI116" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AJ116" t="s">
         <v>40</v>
@@ -49168,10 +49220,10 @@
         <v>131</v>
       </c>
       <c r="AH117" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AI117" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AJ117" t="s">
         <v>40</v>
@@ -49294,10 +49346,10 @@
         <v>131</v>
       </c>
       <c r="AH118" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AI118" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AJ118" t="s">
         <v>40</v>
@@ -49420,16 +49472,16 @@
         <v>131</v>
       </c>
       <c r="AH119" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AI119" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AJ119" s="6" t="s">
         <v>40</v>
       </c>
       <c r="AK119" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AL119" s="6" t="str">
         <f t="shared" si="8"/>
@@ -49549,16 +49601,16 @@
         <v>131</v>
       </c>
       <c r="AH120" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AI120" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AJ120" s="6" t="s">
         <v>40</v>
       </c>
       <c r="AK120" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AL120" s="6" t="str">
         <f t="shared" si="8"/>
@@ -49678,16 +49730,16 @@
         <v>131</v>
       </c>
       <c r="AH121" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AI121" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AJ121" s="6" t="s">
         <v>40</v>
       </c>
       <c r="AK121" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AL121" s="6" t="str">
         <f t="shared" si="8"/>
@@ -49708,7 +49760,7 @@
     </row>
     <row r="331" ht="14.25">
       <c r="L331" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="333" ht="14.25">
@@ -49716,12 +49768,12 @@
         <v>9</v>
       </c>
       <c r="F333" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="334" ht="14.25">
       <c r="A334" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B334" s="12"/>
       <c r="C334" s="12"/>
@@ -49757,26 +49809,26 @@
       <c r="W334" s="8"/>
       <c r="X334" s="8"/>
       <c r="Y334" s="14" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Z334" s="14"/>
       <c r="AA334" s="14"/>
-      <c r="AB334" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC334" s="29"/>
-      <c r="AD334" s="29"/>
-      <c r="AE334" s="29"/>
-      <c r="AF334" s="29"/>
+      <c r="AB334" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC334" s="32"/>
+      <c r="AD334" s="32"/>
+      <c r="AE334" s="32"/>
+      <c r="AF334" s="32"/>
     </row>
     <row r="335" ht="14.25">
       <c r="A335" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B335" s="12"/>
       <c r="C335" s="12"/>
       <c r="D335" s="7" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E335" s="7"/>
       <c r="F335" s="7"/>
@@ -49807,26 +49859,26 @@
       <c r="W335" s="8"/>
       <c r="X335" s="8"/>
       <c r="Y335" s="14" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Z335" s="14"/>
       <c r="AA335" s="14"/>
-      <c r="AB335" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC335" s="29"/>
-      <c r="AD335" s="29"/>
-      <c r="AE335" s="29"/>
-      <c r="AF335" s="29"/>
+      <c r="AB335" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC335" s="32"/>
+      <c r="AD335" s="32"/>
+      <c r="AE335" s="32"/>
+      <c r="AF335" s="32"/>
     </row>
     <row r="336" ht="14.25">
       <c r="A336" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B336" s="12"/>
       <c r="C336" s="12"/>
       <c r="D336" s="7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E336" s="7"/>
       <c r="F336" s="7"/>
@@ -49863,20 +49915,20 @@
       <c r="AA336" s="13"/>
       <c r="AB336" s="13"/>
       <c r="AC336" s="13"/>
-      <c r="AD336" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="AE336" s="32"/>
-      <c r="AF336" s="32"/>
+      <c r="AD336" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="AE336" s="35"/>
+      <c r="AF336" s="35"/>
     </row>
     <row r="337" ht="14.25">
       <c r="A337" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B337" s="12"/>
       <c r="C337" s="12"/>
       <c r="D337" s="7" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E337" s="7"/>
       <c r="F337" s="7"/>
@@ -49903,7 +49955,7 @@
     </row>
     <row r="338" ht="14.25">
       <c r="A338" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B338" s="12"/>
       <c r="C338" s="12"/>
@@ -49921,7 +49973,7 @@
       <c r="K338" s="9"/>
       <c r="L338" s="9"/>
       <c r="M338" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="N338" s="12"/>
       <c r="O338" s="12"/>
@@ -49937,7 +49989,7 @@
       <c r="W338" s="8"/>
       <c r="X338" s="8"/>
       <c r="Y338" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Z338" s="12"/>
       <c r="AA338" s="12"/>
@@ -49949,7 +50001,7 @@
     </row>
     <row r="339" ht="14.25">
       <c r="A339" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B339" s="12"/>
       <c r="C339" s="12"/>
@@ -49967,7 +50019,7 @@
       <c r="K339" s="9"/>
       <c r="L339" s="9"/>
       <c r="M339" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="N339" s="12"/>
       <c r="O339" s="12"/>
@@ -49983,7 +50035,7 @@
       <c r="W339" s="8"/>
       <c r="X339" s="8"/>
       <c r="Y339" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Z339" s="12"/>
       <c r="AA339" s="12"/>
@@ -49995,12 +50047,12 @@
     </row>
     <row r="340" ht="14.25">
       <c r="A340" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B340" s="12"/>
       <c r="C340" s="12"/>
       <c r="D340" s="7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E340" s="7"/>
       <c r="F340" s="7"/>
@@ -50013,7 +50065,7 @@
       <c r="K340" s="9"/>
       <c r="L340" s="9"/>
       <c r="M340" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="N340" s="12"/>
       <c r="O340" s="12"/>
@@ -50025,7 +50077,7 @@
       <c r="S340" s="11"/>
       <c r="T340" s="11"/>
       <c r="U340" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="V340" s="12"/>
       <c r="W340" s="12"/>
@@ -50041,19 +50093,19 @@
     </row>
     <row r="341" ht="14.25">
       <c r="A341" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B341" s="12"/>
       <c r="C341" s="12"/>
       <c r="D341" s="7" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E341" s="7"/>
       <c r="F341" s="7"/>
       <c r="G341" s="7"/>
       <c r="H341" s="7"/>
       <c r="I341" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="J341" s="12"/>
       <c r="K341" s="12"/>
@@ -50071,7 +50123,7 @@
       <c r="S341" s="11"/>
       <c r="T341" s="11"/>
       <c r="U341" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="V341" s="12"/>
       <c r="W341" s="12"/>
@@ -50087,7 +50139,7 @@
     </row>
     <row r="342" ht="14.25">
       <c r="A342" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B342" s="12"/>
       <c r="C342" s="12"/>
@@ -50105,7 +50157,7 @@
       <c r="K342" s="9"/>
       <c r="L342" s="9"/>
       <c r="M342" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="N342" s="12"/>
       <c r="O342" s="12"/>
@@ -50117,7 +50169,7 @@
       <c r="S342" s="11"/>
       <c r="T342" s="11"/>
       <c r="U342" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="V342" s="12"/>
       <c r="W342" s="12"/>
@@ -50125,17 +50177,17 @@
       <c r="Y342" s="12"/>
       <c r="Z342" s="12"/>
       <c r="AA342" s="12"/>
-      <c r="AB342" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC342" s="29"/>
-      <c r="AD342" s="29"/>
-      <c r="AE342" s="29"/>
-      <c r="AF342" s="29"/>
+      <c r="AB342" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC342" s="32"/>
+      <c r="AD342" s="32"/>
+      <c r="AE342" s="32"/>
+      <c r="AF342" s="32"/>
     </row>
     <row r="344" ht="14.25">
       <c r="Q344" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="R344" s="12"/>
       <c r="S344" s="12"/>
@@ -50155,7 +50207,7 @@
     </row>
     <row r="346" ht="14.25">
       <c r="A346" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B346" s="12"/>
       <c r="C346" s="12"/>
@@ -50180,7 +50232,7 @@
       <c r="P346" s="10"/>
       <c r="Q346" s="10"/>
       <c r="R346" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="S346" s="12"/>
       <c r="T346" s="12"/>
@@ -50204,7 +50256,7 @@
     </row>
     <row r="354" ht="14.25">
       <c r="F354" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="355" ht="14.25">
@@ -50269,7 +50321,7 @@
         <v>9</v>
       </c>
       <c r="E367" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AC367" s="6"/>
       <c r="AD367" s="6"/>
@@ -50417,12 +50469,12 @@
     </row>
     <row r="370" ht="14.25">
       <c r="A370" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B370" s="12"/>
       <c r="C370" s="12"/>
       <c r="D370" s="7" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E370" s="7"/>
       <c r="F370" s="7"/>
@@ -50449,30 +50501,30 @@
       <c r="U370" s="11"/>
       <c r="V370" s="11"/>
       <c r="W370" s="11"/>
-      <c r="X370" s="32" t="s">
-        <v>210</v>
+      <c r="X370" s="35" t="s">
+        <v>214</v>
       </c>
       <c r="Y370" s="8" t="s">
         <v>7</v>
       </c>
       <c r="Z370" s="8"/>
       <c r="AA370" s="8"/>
-      <c r="AB370" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC370" s="29"/>
-      <c r="AD370" s="29"/>
-      <c r="AE370" s="29"/>
-      <c r="AF370" s="29"/>
+      <c r="AB370" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC370" s="32"/>
+      <c r="AD370" s="32"/>
+      <c r="AE370" s="32"/>
+      <c r="AF370" s="32"/>
     </row>
     <row r="371" ht="14.25">
       <c r="A371" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B371" s="12"/>
       <c r="C371" s="12"/>
       <c r="D371" s="7" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E371" s="7"/>
       <c r="F371" s="7"/>
@@ -50499,30 +50551,30 @@
       <c r="U371" s="11"/>
       <c r="V371" s="11"/>
       <c r="W371" s="11"/>
-      <c r="X371" s="32" t="s">
-        <v>210</v>
+      <c r="X371" s="35" t="s">
+        <v>214</v>
       </c>
       <c r="Y371" s="8" t="s">
         <v>7</v>
       </c>
       <c r="Z371" s="8"/>
       <c r="AA371" s="8"/>
-      <c r="AB371" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC371" s="29"/>
-      <c r="AD371" s="29"/>
-      <c r="AE371" s="29"/>
-      <c r="AF371" s="29"/>
+      <c r="AB371" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC371" s="32"/>
+      <c r="AD371" s="32"/>
+      <c r="AE371" s="32"/>
+      <c r="AF371" s="32"/>
     </row>
     <row r="372" ht="14.25">
       <c r="A372" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B372" s="12"/>
       <c r="C372" s="12"/>
       <c r="D372" s="7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E372" s="7"/>
       <c r="F372" s="7"/>
@@ -50555,22 +50607,22 @@
       </c>
       <c r="Z372" s="8"/>
       <c r="AA372" s="8"/>
-      <c r="AB372" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC372" s="29"/>
-      <c r="AD372" s="29"/>
-      <c r="AE372" s="29"/>
-      <c r="AF372" s="29"/>
+      <c r="AB372" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC372" s="32"/>
+      <c r="AD372" s="32"/>
+      <c r="AE372" s="32"/>
+      <c r="AF372" s="32"/>
     </row>
     <row r="373" ht="14.25">
       <c r="A373" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B373" s="12"/>
       <c r="C373" s="12"/>
       <c r="D373" s="7" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E373" s="7"/>
       <c r="F373" s="7"/>
@@ -50603,17 +50655,17 @@
       </c>
       <c r="Z373" s="8"/>
       <c r="AA373" s="8"/>
-      <c r="AB373" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC373" s="29"/>
-      <c r="AD373" s="29"/>
-      <c r="AE373" s="29"/>
-      <c r="AF373" s="29"/>
+      <c r="AB373" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC373" s="32"/>
+      <c r="AD373" s="32"/>
+      <c r="AE373" s="32"/>
+      <c r="AF373" s="32"/>
     </row>
     <row r="374" ht="14.25">
       <c r="A374" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B374" s="12"/>
       <c r="C374" s="12"/>
@@ -50659,7 +50711,7 @@
     </row>
     <row r="375" ht="14.25">
       <c r="A375" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B375" s="12"/>
       <c r="C375" s="12"/>
@@ -50705,12 +50757,12 @@
     </row>
     <row r="376" ht="14.25">
       <c r="A376" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B376" s="12"/>
       <c r="C376" s="12"/>
       <c r="D376" s="7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E376" s="7"/>
       <c r="F376" s="7"/>
@@ -50724,7 +50776,7 @@
       <c r="L376" s="9"/>
       <c r="M376" s="9"/>
       <c r="N376" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="O376" s="12"/>
       <c r="P376" s="12"/>
@@ -50738,7 +50790,7 @@
       <c r="V376" s="11"/>
       <c r="W376" s="11"/>
       <c r="X376" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Y376" s="12"/>
       <c r="Z376" s="12"/>
@@ -50751,19 +50803,19 @@
     </row>
     <row r="377" ht="14.25">
       <c r="A377" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B377" s="12"/>
       <c r="C377" s="12"/>
       <c r="D377" s="7" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E377" s="7"/>
       <c r="F377" s="7"/>
       <c r="G377" s="7"/>
       <c r="H377" s="7"/>
       <c r="I377" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="J377" s="12"/>
       <c r="K377" s="12"/>
@@ -50784,7 +50836,7 @@
       <c r="V377" s="11"/>
       <c r="W377" s="11"/>
       <c r="X377" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Y377" s="12"/>
       <c r="Z377" s="12"/>
@@ -50797,7 +50849,7 @@
     </row>
     <row r="378" ht="14.25">
       <c r="A378" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B378" s="12"/>
       <c r="C378" s="12"/>
@@ -50816,7 +50868,7 @@
       <c r="L378" s="9"/>
       <c r="M378" s="9"/>
       <c r="N378" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="O378" s="12"/>
       <c r="P378" s="12"/>
@@ -50829,21 +50881,21 @@
       <c r="U378" s="11"/>
       <c r="V378" s="11"/>
       <c r="W378" s="11"/>
-      <c r="X378" s="32" t="s">
-        <v>210</v>
+      <c r="X378" s="35" t="s">
+        <v>214</v>
       </c>
       <c r="Y378" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Z378" s="12"/>
       <c r="AA378" s="12"/>
-      <c r="AB378" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC378" s="29"/>
-      <c r="AD378" s="29"/>
-      <c r="AE378" s="29"/>
-      <c r="AF378" s="29"/>
+      <c r="AB378" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC378" s="32"/>
+      <c r="AD378" s="32"/>
+      <c r="AE378" s="32"/>
+      <c r="AF378" s="32"/>
     </row>
     <row r="379" ht="14.25">
       <c r="A379" s="6">
@@ -50945,12 +50997,12 @@
     </row>
     <row r="380" ht="14.25">
       <c r="A380" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B380" s="12"/>
       <c r="C380" s="12"/>
       <c r="D380" s="7" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E380" s="7"/>
       <c r="F380" s="7"/>
@@ -50977,26 +51029,26 @@
       <c r="U380" s="11"/>
       <c r="V380" s="11"/>
       <c r="W380" s="11"/>
-      <c r="X380" s="32" t="s">
-        <v>210</v>
+      <c r="X380" s="35" t="s">
+        <v>214</v>
       </c>
       <c r="Y380" s="8" t="s">
         <v>7</v>
       </c>
       <c r="Z380" s="8"/>
       <c r="AA380" s="8"/>
-      <c r="AB380" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC380" s="29"/>
-      <c r="AD380" s="29"/>
-      <c r="AE380" s="29"/>
-      <c r="AF380" s="29"/>
+      <c r="AB380" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC380" s="32"/>
+      <c r="AD380" s="32"/>
+      <c r="AE380" s="32"/>
+      <c r="AF380" s="32"/>
       <c r="AG380" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="AH380" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AQ380" t="s">
         <v>76</v>
@@ -51036,25 +51088,25 @@
       <c r="U381" s="5"/>
       <c r="V381" s="5"/>
       <c r="W381" s="5"/>
-      <c r="X381" s="29">
+      <c r="X381" s="32">
         <v>0</v>
       </c>
       <c r="Y381" s="5"/>
       <c r="Z381" s="5"/>
       <c r="AA381" s="5"/>
-      <c r="AB381" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC381" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD381" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE381" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF381" s="29">
+      <c r="AB381" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC381" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD381" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE381" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF381" s="32">
         <v>0</v>
       </c>
       <c r="AG381" s="5">
@@ -51063,11 +51115,11 @@
       <c r="AH381" t="s">
         <v>135</v>
       </c>
-      <c r="AI381" s="33" t="s">
-        <v>211</v>
+      <c r="AI381" s="36" t="s">
+        <v>215</v>
       </c>
       <c r="AJ381" s="6" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AK381" s="6"/>
       <c r="AL381" s="6"/>
@@ -51099,34 +51151,34 @@
       <c r="U382" s="5"/>
       <c r="V382" s="5"/>
       <c r="W382" s="5"/>
-      <c r="X382" s="29">
+      <c r="X382" s="32">
         <v>0</v>
       </c>
       <c r="Y382" s="5"/>
       <c r="Z382" s="5"/>
       <c r="AA382" s="5"/>
-      <c r="AB382" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC382" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD382" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE382" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF382" s="29">
+      <c r="AB382" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC382" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD382" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE382" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF382" s="32">
         <v>1</v>
       </c>
       <c r="AG382" s="5">
         <v>1</v>
       </c>
       <c r="AH382" t="s">
-        <v>213</v>
-      </c>
-      <c r="AI382" s="33"/>
+        <v>217</v>
+      </c>
+      <c r="AI382" s="36"/>
       <c r="AJ382" s="6"/>
       <c r="AK382" s="6"/>
       <c r="AL382" s="6"/>
@@ -51158,34 +51210,34 @@
       <c r="U383" s="5"/>
       <c r="V383" s="5"/>
       <c r="W383" s="5"/>
-      <c r="X383" s="29">
+      <c r="X383" s="32">
         <v>0</v>
       </c>
       <c r="Y383" s="5"/>
       <c r="Z383" s="5"/>
       <c r="AA383" s="5"/>
-      <c r="AB383" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC383" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD383" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE383" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF383" s="29">
+      <c r="AB383" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC383" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD383" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE383" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF383" s="32">
         <v>0</v>
       </c>
       <c r="AG383" s="5">
         <v>2</v>
       </c>
       <c r="AH383" t="s">
-        <v>215</v>
-      </c>
-      <c r="AI383" s="33"/>
+        <v>219</v>
+      </c>
+      <c r="AI383" s="36"/>
       <c r="AJ383" s="6"/>
       <c r="AK383" s="6"/>
       <c r="AL383" s="6"/>
@@ -51217,34 +51269,34 @@
       <c r="U384" s="5"/>
       <c r="V384" s="5"/>
       <c r="W384" s="5"/>
-      <c r="X384" s="29">
+      <c r="X384" s="32">
         <v>0</v>
       </c>
       <c r="Y384" s="5"/>
       <c r="Z384" s="5"/>
       <c r="AA384" s="5"/>
-      <c r="AB384" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC384" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD384" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE384" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF384" s="29">
+      <c r="AB384" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC384" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD384" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE384" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF384" s="32">
         <v>1</v>
       </c>
       <c r="AG384" s="5">
         <v>3</v>
       </c>
       <c r="AH384" t="s">
-        <v>216</v>
-      </c>
-      <c r="AI384" s="33"/>
+        <v>220</v>
+      </c>
+      <c r="AI384" s="36"/>
       <c r="AJ384" s="6"/>
       <c r="AK384" s="6"/>
       <c r="AL384" s="6"/>
@@ -51276,25 +51328,25 @@
       <c r="U385" s="5"/>
       <c r="V385" s="5"/>
       <c r="W385" s="5"/>
-      <c r="X385" s="29">
+      <c r="X385" s="32">
         <v>0</v>
       </c>
       <c r="Y385" s="5"/>
       <c r="Z385" s="5"/>
       <c r="AA385" s="5"/>
-      <c r="AB385" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC385" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD385" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE385" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF385" s="29">
+      <c r="AB385" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC385" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD385" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE385" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF385" s="32">
         <v>0</v>
       </c>
       <c r="AG385" s="5">
@@ -51335,25 +51387,25 @@
       <c r="U386" s="5"/>
       <c r="V386" s="5"/>
       <c r="W386" s="5"/>
-      <c r="X386" s="29">
+      <c r="X386" s="32">
         <v>0</v>
       </c>
       <c r="Y386" s="5"/>
       <c r="Z386" s="5"/>
       <c r="AA386" s="5"/>
-      <c r="AB386" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC386" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD386" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE386" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF386" s="29">
+      <c r="AB386" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC386" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD386" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE386" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF386" s="32">
         <v>1</v>
       </c>
       <c r="AG386" s="5">
@@ -51391,25 +51443,25 @@
       <c r="U387" s="5"/>
       <c r="V387" s="5"/>
       <c r="W387" s="5"/>
-      <c r="X387" s="29">
+      <c r="X387" s="32">
         <v>0</v>
       </c>
       <c r="Y387" s="5"/>
       <c r="Z387" s="5"/>
       <c r="AA387" s="5"/>
-      <c r="AB387" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC387" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD387" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE387" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF387" s="29">
+      <c r="AB387" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC387" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD387" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE387" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF387" s="32">
         <v>0</v>
       </c>
       <c r="AG387" s="5">
@@ -51447,25 +51499,25 @@
       <c r="U388" s="5"/>
       <c r="V388" s="5"/>
       <c r="W388" s="5"/>
-      <c r="X388" s="29">
+      <c r="X388" s="32">
         <v>0</v>
       </c>
       <c r="Y388" s="5"/>
       <c r="Z388" s="5"/>
       <c r="AA388" s="5"/>
-      <c r="AB388" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC388" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD388" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE388" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF388" s="29">
+      <c r="AB388" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC388" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD388" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE388" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF388" s="32">
         <v>1</v>
       </c>
       <c r="AG388" s="5">
@@ -51503,25 +51555,25 @@
       <c r="U389" s="5"/>
       <c r="V389" s="5"/>
       <c r="W389" s="5"/>
-      <c r="X389" s="29">
+      <c r="X389" s="32">
         <v>0</v>
       </c>
       <c r="Y389" s="5"/>
       <c r="Z389" s="5"/>
       <c r="AA389" s="5"/>
-      <c r="AB389" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC389" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD389" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE389" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF389" s="29">
+      <c r="AB389" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC389" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD389" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE389" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF389" s="32">
         <v>0</v>
       </c>
       <c r="AG389" s="5">
@@ -51558,32 +51610,32 @@
       <c r="U390" s="5"/>
       <c r="V390" s="5"/>
       <c r="W390" s="5"/>
-      <c r="X390" s="29">
+      <c r="X390" s="32">
         <v>0</v>
       </c>
       <c r="Y390" s="5"/>
       <c r="Z390" s="5"/>
       <c r="AA390" s="5"/>
-      <c r="AB390" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC390" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD390" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE390" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF390" s="29">
+      <c r="AB390" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC390" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD390" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE390" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF390" s="32">
         <v>1</v>
       </c>
       <c r="AG390" s="5">
         <v>9</v>
       </c>
       <c r="AH390" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AI390" s="6"/>
       <c r="AJ390" s="6"/>
@@ -51614,29 +51666,29 @@
       <c r="U391" s="5"/>
       <c r="V391" s="5"/>
       <c r="W391" s="5"/>
-      <c r="X391" s="29">
+      <c r="X391" s="32">
         <v>0</v>
       </c>
       <c r="Y391" s="5"/>
       <c r="Z391" s="5"/>
       <c r="AA391" s="5"/>
-      <c r="AB391" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC391" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD391" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE391" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF391" s="29">
+      <c r="AB391" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC391" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD391" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE391" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF391" s="32">
         <v>0</v>
       </c>
       <c r="AG391" s="5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AI391" s="6"/>
       <c r="AJ391" s="6"/>
@@ -51667,32 +51719,32 @@
       <c r="U392" s="5"/>
       <c r="V392" s="5"/>
       <c r="W392" s="5"/>
-      <c r="X392" s="29">
+      <c r="X392" s="32">
         <v>0</v>
       </c>
       <c r="Y392" s="5"/>
       <c r="Z392" s="5"/>
       <c r="AA392" s="5"/>
-      <c r="AB392" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC392" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD392" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE392" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF392" s="29">
+      <c r="AB392" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC392" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD392" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE392" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF392" s="32">
         <v>1</v>
       </c>
       <c r="AG392" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AH392" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AJ392" s="6"/>
       <c r="AK392" s="6"/>
@@ -51722,32 +51774,32 @@
       <c r="U393" s="5"/>
       <c r="V393" s="5"/>
       <c r="W393" s="5"/>
-      <c r="X393" s="29">
+      <c r="X393" s="32">
         <v>0</v>
       </c>
       <c r="Y393" s="5"/>
       <c r="Z393" s="5"/>
       <c r="AA393" s="5"/>
-      <c r="AB393" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC393" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD393" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE393" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF393" s="29">
+      <c r="AB393" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC393" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD393" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE393" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF393" s="32">
         <v>0</v>
       </c>
       <c r="AG393" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AH393" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AJ393" s="6"/>
       <c r="AK393" s="6"/>
@@ -51777,29 +51829,29 @@
       <c r="U394" s="5"/>
       <c r="V394" s="5"/>
       <c r="W394" s="5"/>
-      <c r="X394" s="29">
+      <c r="X394" s="32">
         <v>0</v>
       </c>
       <c r="Y394" s="5"/>
       <c r="Z394" s="5"/>
       <c r="AA394" s="5"/>
-      <c r="AB394" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC394" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD394" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE394" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF394" s="29">
+      <c r="AB394" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC394" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD394" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE394" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF394" s="32">
         <v>1</v>
       </c>
       <c r="AG394" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AI394" s="6"/>
       <c r="AJ394" s="6"/>
@@ -51830,32 +51882,32 @@
       <c r="U395" s="5"/>
       <c r="V395" s="5"/>
       <c r="W395" s="5"/>
-      <c r="X395" s="29">
+      <c r="X395" s="32">
         <v>0</v>
       </c>
       <c r="Y395" s="5"/>
       <c r="Z395" s="5"/>
       <c r="AA395" s="5"/>
-      <c r="AB395" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC395" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD395" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE395" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF395" s="29">
+      <c r="AB395" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC395" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD395" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE395" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF395" s="32">
         <v>0</v>
       </c>
       <c r="AG395" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="AH395" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="AI395" s="6"/>
       <c r="AJ395" s="6"/>
@@ -51886,32 +51938,32 @@
       <c r="U396" s="5"/>
       <c r="V396" s="5"/>
       <c r="W396" s="5"/>
-      <c r="X396" s="29">
+      <c r="X396" s="32">
         <v>0</v>
       </c>
       <c r="Y396" s="5"/>
       <c r="Z396" s="5"/>
       <c r="AA396" s="5"/>
-      <c r="AB396" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC396" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD396" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE396" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF396" s="29">
+      <c r="AB396" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC396" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD396" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE396" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF396" s="32">
         <v>1</v>
       </c>
       <c r="AG396" s="5" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AH396" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="AI396" s="6"/>
       <c r="AJ396" s="6"/>
@@ -51942,19 +51994,19 @@
       <c r="U397" s="5"/>
       <c r="V397" s="5"/>
       <c r="W397" s="5"/>
-      <c r="X397" s="29">
+      <c r="X397" s="32">
         <v>1</v>
       </c>
       <c r="Y397" s="5"/>
       <c r="Z397" s="5"/>
       <c r="AA397" s="5"/>
-      <c r="AB397" s="29" t="s">
-        <v>259</v>
-      </c>
-      <c r="AC397" s="29"/>
-      <c r="AD397" s="29"/>
-      <c r="AE397" s="29"/>
-      <c r="AF397" s="29"/>
+      <c r="AB397" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="AC397" s="32"/>
+      <c r="AD397" s="32"/>
+      <c r="AE397" s="32"/>
+      <c r="AF397" s="32"/>
       <c r="AG397" s="5"/>
       <c r="AH397" s="6" t="s">
         <v>15</v>
@@ -52063,12 +52115,12 @@
     </row>
     <row r="399" ht="14.25">
       <c r="A399" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B399" s="12"/>
       <c r="C399" s="12"/>
       <c r="D399" s="7" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E399" s="7"/>
       <c r="F399" s="7"/>
@@ -52095,21 +52147,21 @@
       <c r="U399" s="11"/>
       <c r="V399" s="11"/>
       <c r="W399" s="11"/>
-      <c r="X399" s="32" t="s">
-        <v>210</v>
+      <c r="X399" s="35" t="s">
+        <v>214</v>
       </c>
       <c r="Y399" s="8" t="s">
         <v>7</v>
       </c>
       <c r="Z399" s="8"/>
       <c r="AA399" s="8"/>
-      <c r="AB399" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC399" s="29"/>
-      <c r="AD399" s="29"/>
-      <c r="AE399" s="29"/>
-      <c r="AF399" s="29"/>
+      <c r="AB399" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC399" s="32"/>
+      <c r="AD399" s="32"/>
+      <c r="AE399" s="32"/>
+      <c r="AF399" s="32"/>
     </row>
     <row r="400" ht="14.25">
       <c r="A400" s="6">
@@ -52211,12 +52263,12 @@
     </row>
     <row r="401" ht="14.25">
       <c r="A401" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B401" s="12"/>
       <c r="C401" s="12"/>
       <c r="D401" s="7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E401" s="7"/>
       <c r="F401" s="7"/>
@@ -52249,15 +52301,15 @@
       </c>
       <c r="Z401" s="8"/>
       <c r="AA401" s="8"/>
-      <c r="AB401" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC401" s="29"/>
-      <c r="AD401" s="29"/>
-      <c r="AE401" s="29"/>
-      <c r="AF401" s="29"/>
+      <c r="AB401" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC401" s="32"/>
+      <c r="AD401" s="32"/>
+      <c r="AE401" s="32"/>
+      <c r="AF401" s="32"/>
       <c r="AH401" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="402" ht="14.25">
@@ -52290,7 +52342,7 @@
       <c r="Q402" s="5"/>
       <c r="R402" s="5"/>
       <c r="S402" s="14" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="T402" s="14"/>
       <c r="U402" s="14"/>
@@ -52306,7 +52358,7 @@
       <c r="AE402" s="17"/>
       <c r="AF402" s="17"/>
       <c r="AH402" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="403" ht="14.25">
@@ -52409,12 +52461,12 @@
     </row>
     <row r="404" ht="14.25">
       <c r="A404" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B404" s="12"/>
       <c r="C404" s="12"/>
       <c r="D404" s="7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E404" s="7"/>
       <c r="F404" s="7"/>
@@ -52447,29 +52499,29 @@
       </c>
       <c r="Z404" s="8"/>
       <c r="AA404" s="8"/>
-      <c r="AB404" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC404" s="29"/>
-      <c r="AD404" s="29"/>
-      <c r="AE404" s="29"/>
-      <c r="AF404" s="29"/>
+      <c r="AB404" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC404" s="32"/>
+      <c r="AD404" s="32"/>
+      <c r="AE404" s="32"/>
+      <c r="AF404" s="32"/>
     </row>
     <row r="405" ht="14.25">
       <c r="A405" s="5"/>
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
       <c r="D405" s="7" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E405" s="7" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F405" s="7" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="G405" s="7" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="H405" s="7">
         <v>1</v>
@@ -52485,7 +52537,7 @@
       <c r="Q405" s="5"/>
       <c r="R405" s="5"/>
       <c r="S405" s="14" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="T405" s="14"/>
       <c r="U405" s="14"/>
@@ -52601,7 +52653,7 @@
     </row>
     <row r="407" ht="14.25">
       <c r="A407" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B407" s="12"/>
       <c r="C407" s="12"/>
@@ -52669,25 +52721,25 @@
       <c r="K408" s="5"/>
       <c r="L408" s="5"/>
       <c r="M408" s="5"/>
-      <c r="N408" s="28"/>
-      <c r="O408" s="28"/>
-      <c r="P408" s="28"/>
-      <c r="Q408" s="28"/>
-      <c r="R408" s="28"/>
-      <c r="S408" s="28"/>
-      <c r="T408" s="28"/>
-      <c r="U408" s="28"/>
-      <c r="V408" s="28"/>
-      <c r="W408" s="28"/>
-      <c r="X408" s="28"/>
+      <c r="N408" s="31"/>
+      <c r="O408" s="31"/>
+      <c r="P408" s="31"/>
+      <c r="Q408" s="31"/>
+      <c r="R408" s="31"/>
+      <c r="S408" s="31"/>
+      <c r="T408" s="31"/>
+      <c r="U408" s="31"/>
+      <c r="V408" s="31"/>
+      <c r="W408" s="31"/>
+      <c r="X408" s="31"/>
       <c r="Y408" s="5"/>
       <c r="Z408" s="5"/>
       <c r="AA408" s="5"/>
-      <c r="AB408" s="28"/>
-      <c r="AC408" s="28"/>
-      <c r="AD408" s="28"/>
-      <c r="AE408" s="28"/>
-      <c r="AF408" s="28"/>
+      <c r="AB408" s="31"/>
+      <c r="AC408" s="31"/>
+      <c r="AD408" s="31"/>
+      <c r="AE408" s="31"/>
+      <c r="AF408" s="31"/>
     </row>
     <row r="409" ht="14.25">
       <c r="A409" s="6">
@@ -52789,7 +52841,7 @@
     </row>
     <row r="410" ht="14.25">
       <c r="A410" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B410" s="12"/>
       <c r="C410" s="12"/>
@@ -52857,25 +52909,25 @@
       <c r="K411" s="5"/>
       <c r="L411" s="5"/>
       <c r="M411" s="5"/>
-      <c r="N411" s="28"/>
-      <c r="O411" s="28"/>
-      <c r="P411" s="28"/>
-      <c r="Q411" s="28"/>
-      <c r="R411" s="28"/>
-      <c r="S411" s="28"/>
-      <c r="T411" s="28"/>
-      <c r="U411" s="28"/>
-      <c r="V411" s="28"/>
-      <c r="W411" s="28"/>
-      <c r="X411" s="28"/>
+      <c r="N411" s="31"/>
+      <c r="O411" s="31"/>
+      <c r="P411" s="31"/>
+      <c r="Q411" s="31"/>
+      <c r="R411" s="31"/>
+      <c r="S411" s="31"/>
+      <c r="T411" s="31"/>
+      <c r="U411" s="31"/>
+      <c r="V411" s="31"/>
+      <c r="W411" s="31"/>
+      <c r="X411" s="31"/>
       <c r="Y411" s="5"/>
       <c r="Z411" s="5"/>
       <c r="AA411" s="5"/>
-      <c r="AB411" s="28"/>
-      <c r="AC411" s="28"/>
-      <c r="AD411" s="28"/>
-      <c r="AE411" s="28"/>
-      <c r="AF411" s="28"/>
+      <c r="AB411" s="31"/>
+      <c r="AC411" s="31"/>
+      <c r="AD411" s="31"/>
+      <c r="AE411" s="31"/>
+      <c r="AF411" s="31"/>
     </row>
     <row r="412" ht="14.25">
       <c r="A412" s="6">
@@ -52977,12 +53029,12 @@
     </row>
     <row r="413" ht="14.25">
       <c r="A413" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B413" s="12"/>
       <c r="C413" s="12"/>
       <c r="D413" s="7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E413" s="7"/>
       <c r="F413" s="7"/>
@@ -52996,7 +53048,7 @@
       <c r="L413" s="9"/>
       <c r="M413" s="9"/>
       <c r="N413" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="O413" s="12"/>
       <c r="P413" s="12"/>
@@ -53010,7 +53062,7 @@
       <c r="V413" s="11"/>
       <c r="W413" s="11"/>
       <c r="X413" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Y413" s="12"/>
       <c r="Z413" s="12"/>
@@ -53067,20 +53119,20 @@
     </row>
     <row r="415" ht="14.25">
       <c r="N415" s="12" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O415" s="12"/>
       <c r="P415" s="12" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q415" s="12"/>
       <c r="R415" s="12"/>
       <c r="X415" s="12" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Y415" s="12"/>
       <c r="Z415" s="12" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AA415" s="12"/>
       <c r="AB415" s="12"/>
@@ -53119,19 +53171,19 @@
     </row>
     <row r="418" ht="14.25">
       <c r="N418" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="O418" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="P418" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q418" t="s">
+        <v>274</v>
+      </c>
+      <c r="R418" t="s">
         <v>270</v>
-      </c>
-      <c r="R418" t="s">
-        <v>266</v>
       </c>
       <c r="Z418" t="s">
         <v>98</v>
@@ -53139,18 +53191,18 @@
     </row>
     <row r="419" ht="14.25">
       <c r="R419" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Z419" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="420" ht="14.25">
       <c r="R420" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="T420" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="422" ht="14.25">
@@ -53253,19 +53305,19 @@
     </row>
     <row r="423" ht="14.25">
       <c r="A423" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B423" s="12"/>
       <c r="C423" s="12"/>
       <c r="D423" s="7" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E423" s="7"/>
       <c r="F423" s="7"/>
       <c r="G423" s="7"/>
       <c r="H423" s="7"/>
       <c r="I423" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="J423" s="12"/>
       <c r="K423" s="12"/>
@@ -53286,7 +53338,7 @@
       <c r="V423" s="11"/>
       <c r="W423" s="11"/>
       <c r="X423" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Y423" s="12"/>
       <c r="Z423" s="12"/>
@@ -53343,11 +53395,11 @@
     </row>
     <row r="425" ht="14.25">
       <c r="I425" s="12" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J425" s="12"/>
       <c r="K425" s="12" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L425" s="12"/>
       <c r="M425" s="12"/>
@@ -53364,15 +53416,15 @@
     </row>
     <row r="427" ht="14.25">
       <c r="X427" s="12" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Y427" s="12"/>
       <c r="Z427" s="14" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AA427" s="14"/>
       <c r="AB427" s="12" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AC427" s="12"/>
       <c r="AD427" s="12"/>
@@ -53401,10 +53453,10 @@
       <c r="Y428" s="13">
         <v>0</v>
       </c>
-      <c r="Z428" s="28">
-        <v>0</v>
-      </c>
-      <c r="AA428" s="28">
+      <c r="Z428" s="31">
+        <v>0</v>
+      </c>
+      <c r="AA428" s="31">
         <v>0</v>
       </c>
       <c r="AB428" t="s">
@@ -53425,14 +53477,14 @@
       <c r="Y429" s="13">
         <v>1</v>
       </c>
-      <c r="Z429" s="28">
-        <v>0</v>
-      </c>
-      <c r="AA429" s="28">
+      <c r="Z429" s="31">
+        <v>0</v>
+      </c>
+      <c r="AA429" s="31">
         <v>1</v>
       </c>
       <c r="AB429" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AC429" s="5"/>
       <c r="AD429" s="5"/>
@@ -53449,14 +53501,14 @@
       <c r="Y430" s="13">
         <v>0</v>
       </c>
-      <c r="Z430" s="28">
-        <v>1</v>
-      </c>
-      <c r="AA430" s="28">
+      <c r="Z430" s="31">
+        <v>1</v>
+      </c>
+      <c r="AA430" s="31">
         <v>0</v>
       </c>
       <c r="AB430" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="AC430" s="5"/>
       <c r="AD430" s="5"/>
@@ -53465,7 +53517,7 @@
     </row>
     <row r="431" ht="14.25">
       <c r="W431" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="X431" s="13">
         <v>1</v>
@@ -53473,14 +53525,14 @@
       <c r="Y431" s="13">
         <v>1</v>
       </c>
-      <c r="Z431" s="28">
-        <v>1</v>
-      </c>
-      <c r="AA431" s="28">
+      <c r="Z431" s="31">
+        <v>1</v>
+      </c>
+      <c r="AA431" s="31">
         <v>1</v>
       </c>
       <c r="AB431" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AC431" s="5"/>
       <c r="AD431" s="5"/>
@@ -53587,7 +53639,7 @@
     </row>
     <row r="435" ht="14.25">
       <c r="A435" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B435" s="12"/>
       <c r="C435" s="12"/>
@@ -53606,7 +53658,7 @@
       <c r="L435" s="9"/>
       <c r="M435" s="9"/>
       <c r="N435" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="O435" s="12"/>
       <c r="P435" s="12"/>
@@ -53619,21 +53671,21 @@
       <c r="U435" s="11"/>
       <c r="V435" s="11"/>
       <c r="W435" s="11"/>
-      <c r="X435" s="32" t="s">
-        <v>210</v>
+      <c r="X435" s="35" t="s">
+        <v>214</v>
       </c>
       <c r="Y435" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Z435" s="12"/>
       <c r="AA435" s="12"/>
-      <c r="AB435" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC435" s="29"/>
-      <c r="AD435" s="29"/>
-      <c r="AE435" s="29"/>
-      <c r="AF435" s="29"/>
+      <c r="AB435" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC435" s="32"/>
+      <c r="AD435" s="32"/>
+      <c r="AE435" s="32"/>
+      <c r="AF435" s="32"/>
     </row>
     <row r="436" ht="14.25">
       <c r="A436" s="5"/>
@@ -53671,17 +53723,17 @@
       <c r="U436" s="5"/>
       <c r="V436" s="5"/>
       <c r="W436" s="5"/>
-      <c r="X436" s="32"/>
+      <c r="X436" s="35"/>
       <c r="Y436" s="13"/>
       <c r="Z436" s="13"/>
       <c r="AA436" s="13"/>
-      <c r="AB436" s="29" t="s">
-        <v>277</v>
-      </c>
-      <c r="AC436" s="29"/>
-      <c r="AD436" s="29"/>
-      <c r="AE436" s="29"/>
-      <c r="AF436" s="29"/>
+      <c r="AB436" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="AC436" s="32"/>
+      <c r="AD436" s="32"/>
+      <c r="AE436" s="32"/>
+      <c r="AF436" s="32"/>
     </row>
     <row r="437" ht="14.25">
       <c r="A437" s="5"/>
@@ -53709,25 +53761,25 @@
       <c r="U437" s="5"/>
       <c r="V437" s="5"/>
       <c r="W437" s="5"/>
-      <c r="X437" s="32">
+      <c r="X437" s="35">
         <v>0</v>
       </c>
       <c r="Y437" s="13"/>
       <c r="Z437" s="13"/>
       <c r="AA437" s="13"/>
-      <c r="AB437" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC437" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD437" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE437" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF437" s="29">
+      <c r="AB437" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC437" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD437" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE437" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF437" s="32">
         <v>0</v>
       </c>
     </row>
@@ -53765,15 +53817,15 @@
       <c r="U438" s="5"/>
       <c r="V438" s="5"/>
       <c r="W438" s="5"/>
-      <c r="X438" s="32"/>
+      <c r="X438" s="35"/>
       <c r="Y438" s="13"/>
       <c r="Z438" s="13"/>
       <c r="AA438" s="13"/>
-      <c r="AB438" s="29"/>
-      <c r="AC438" s="29"/>
-      <c r="AD438" s="29"/>
-      <c r="AE438" s="29"/>
-      <c r="AF438" s="29"/>
+      <c r="AB438" s="32"/>
+      <c r="AC438" s="32"/>
+      <c r="AD438" s="32"/>
+      <c r="AE438" s="32"/>
+      <c r="AF438" s="32"/>
       <c r="AH438" t="s">
         <v>87</v>
       </c>
@@ -53812,15 +53864,15 @@
       <c r="U439" s="5"/>
       <c r="V439" s="5"/>
       <c r="W439" s="5"/>
-      <c r="X439" s="32"/>
+      <c r="X439" s="35"/>
       <c r="Y439" s="13"/>
       <c r="Z439" s="13"/>
       <c r="AA439" s="13"/>
-      <c r="AB439" s="29"/>
-      <c r="AC439" s="29"/>
-      <c r="AD439" s="29"/>
-      <c r="AE439" s="29"/>
-      <c r="AF439" s="29"/>
+      <c r="AB439" s="32"/>
+      <c r="AC439" s="32"/>
+      <c r="AD439" s="32"/>
+      <c r="AE439" s="32"/>
+      <c r="AF439" s="32"/>
       <c r="AH439" t="s">
         <v>91</v>
       </c>
@@ -53862,15 +53914,15 @@
       <c r="U440" s="5"/>
       <c r="V440" s="5"/>
       <c r="W440" s="5"/>
-      <c r="X440" s="32"/>
+      <c r="X440" s="35"/>
       <c r="Y440" s="13"/>
       <c r="Z440" s="13"/>
       <c r="AA440" s="13"/>
-      <c r="AB440" s="29"/>
-      <c r="AC440" s="29"/>
-      <c r="AD440" s="29"/>
-      <c r="AE440" s="29"/>
-      <c r="AF440" s="29"/>
+      <c r="AB440" s="32"/>
+      <c r="AC440" s="32"/>
+      <c r="AD440" s="32"/>
+      <c r="AE440" s="32"/>
+      <c r="AF440" s="32"/>
       <c r="AH440" t="s">
         <v>96</v>
       </c>
@@ -53912,15 +53964,15 @@
       <c r="U441" s="5"/>
       <c r="V441" s="5"/>
       <c r="W441" s="5"/>
-      <c r="X441" s="32"/>
+      <c r="X441" s="35"/>
       <c r="Y441" s="13"/>
       <c r="Z441" s="13"/>
       <c r="AA441" s="13"/>
-      <c r="AB441" s="29"/>
-      <c r="AC441" s="29"/>
-      <c r="AD441" s="29"/>
-      <c r="AE441" s="29"/>
-      <c r="AF441" s="29"/>
+      <c r="AB441" s="32"/>
+      <c r="AC441" s="32"/>
+      <c r="AD441" s="32"/>
+      <c r="AE441" s="32"/>
+      <c r="AF441" s="32"/>
       <c r="AH441" t="s">
         <v>100</v>
       </c>
@@ -53959,15 +54011,15 @@
       <c r="U442" s="5"/>
       <c r="V442" s="5"/>
       <c r="W442" s="5"/>
-      <c r="X442" s="32"/>
+      <c r="X442" s="35"/>
       <c r="Y442" s="13"/>
       <c r="Z442" s="13"/>
       <c r="AA442" s="13"/>
-      <c r="AB442" s="29"/>
-      <c r="AC442" s="29"/>
-      <c r="AD442" s="29"/>
-      <c r="AE442" s="29"/>
-      <c r="AF442" s="29"/>
+      <c r="AB442" s="32"/>
+      <c r="AC442" s="32"/>
+      <c r="AD442" s="32"/>
+      <c r="AE442" s="32"/>
+      <c r="AF442" s="32"/>
       <c r="AH442" t="s">
         <v>103</v>
       </c>
@@ -54006,15 +54058,15 @@
       <c r="U443" s="5"/>
       <c r="V443" s="5"/>
       <c r="W443" s="5"/>
-      <c r="X443" s="32"/>
+      <c r="X443" s="35"/>
       <c r="Y443" s="13"/>
       <c r="Z443" s="13"/>
       <c r="AA443" s="13"/>
-      <c r="AB443" s="29"/>
-      <c r="AC443" s="29"/>
-      <c r="AD443" s="29"/>
-      <c r="AE443" s="29"/>
-      <c r="AF443" s="29"/>
+      <c r="AB443" s="32"/>
+      <c r="AC443" s="32"/>
+      <c r="AD443" s="32"/>
+      <c r="AE443" s="32"/>
+      <c r="AF443" s="32"/>
     </row>
     <row r="444" ht="14.25">
       <c r="A444" s="5"/>
@@ -54050,15 +54102,15 @@
       <c r="U444" s="5"/>
       <c r="V444" s="5"/>
       <c r="W444" s="5"/>
-      <c r="X444" s="32"/>
+      <c r="X444" s="35"/>
       <c r="Y444" s="13"/>
       <c r="Z444" s="13"/>
       <c r="AA444" s="13"/>
-      <c r="AB444" s="29"/>
-      <c r="AC444" s="29"/>
-      <c r="AD444" s="29"/>
-      <c r="AE444" s="29"/>
-      <c r="AF444" s="29"/>
+      <c r="AB444" s="32"/>
+      <c r="AC444" s="32"/>
+      <c r="AD444" s="32"/>
+      <c r="AE444" s="32"/>
+      <c r="AF444" s="32"/>
     </row>
     <row r="445" ht="14.25">
       <c r="A445" s="5"/>
@@ -54094,15 +54146,15 @@
       <c r="U445" s="5"/>
       <c r="V445" s="5"/>
       <c r="W445" s="5"/>
-      <c r="X445" s="32"/>
+      <c r="X445" s="35"/>
       <c r="Y445" s="13"/>
       <c r="Z445" s="13"/>
       <c r="AA445" s="13"/>
-      <c r="AB445" s="29"/>
-      <c r="AC445" s="29"/>
-      <c r="AD445" s="29"/>
-      <c r="AE445" s="29"/>
-      <c r="AF445" s="29"/>
+      <c r="AB445" s="32"/>
+      <c r="AC445" s="32"/>
+      <c r="AD445" s="32"/>
+      <c r="AE445" s="32"/>
+      <c r="AF445" s="32"/>
     </row>
     <row r="450" ht="14.25">
       <c r="A450" s="5"/>
@@ -54121,7 +54173,7 @@
     </row>
     <row r="451" ht="14.25">
       <c r="AH451" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AI451" t="s">
         <v>114</v>
@@ -54182,17 +54234,17 @@
       <c r="AJ458" s="6"/>
     </row>
     <row r="459" ht="14.25">
-      <c r="X459" s="32"/>
+      <c r="X459" s="35"/>
       <c r="Y459" s="13"/>
       <c r="Z459" s="13"/>
       <c r="AA459" s="13"/>
-      <c r="AB459" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC459" s="29"/>
-      <c r="AD459" s="29"/>
-      <c r="AE459" s="29"/>
-      <c r="AF459" s="29"/>
+      <c r="AB459" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="AC459" s="32"/>
+      <c r="AD459" s="32"/>
+      <c r="AE459" s="32"/>
+      <c r="AF459" s="32"/>
       <c r="AI459" t="s">
         <v>127</v>
       </c>
@@ -54201,23 +54253,23 @@
       </c>
     </row>
     <row r="460" ht="14.25">
-      <c r="X460" s="32"/>
+      <c r="X460" s="35"/>
       <c r="Y460" s="13"/>
       <c r="Z460" s="13"/>
       <c r="AA460" s="13"/>
-      <c r="AB460" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC460" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD460" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE460" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF460" s="29">
+      <c r="AB460" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC460" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD460" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE460" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF460" s="32">
         <v>1</v>
       </c>
       <c r="AI460" t="s">
@@ -54228,23 +54280,23 @@
       </c>
     </row>
     <row r="461" ht="14.25">
-      <c r="X461" s="32"/>
+      <c r="X461" s="35"/>
       <c r="Y461" s="13"/>
       <c r="Z461" s="13"/>
       <c r="AA461" s="13"/>
-      <c r="AB461" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC461" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD461" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE461" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF461" s="29">
+      <c r="AB461" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC461" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD461" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE461" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF461" s="32">
         <v>0</v>
       </c>
       <c r="AI461" t="s">
@@ -54255,23 +54307,23 @@
       </c>
     </row>
     <row r="462" ht="14.25">
-      <c r="X462" s="32"/>
+      <c r="X462" s="35"/>
       <c r="Y462" s="13"/>
       <c r="Z462" s="13"/>
       <c r="AA462" s="13"/>
-      <c r="AB462" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC462" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD462" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE462" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF462" s="29">
+      <c r="AB462" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC462" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD462" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE462" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF462" s="32">
         <v>1</v>
       </c>
       <c r="AI462" t="s">
@@ -54280,23 +54332,23 @@
       <c r="AJ462" s="6"/>
     </row>
     <row r="463" ht="14.25">
-      <c r="X463" s="32"/>
+      <c r="X463" s="35"/>
       <c r="Y463" s="13"/>
       <c r="Z463" s="13"/>
       <c r="AA463" s="13"/>
-      <c r="AB463" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC463" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD463" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE463" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF463" s="29">
+      <c r="AB463" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC463" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD463" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE463" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF463" s="32">
         <v>0</v>
       </c>
       <c r="AI463" t="s">
@@ -54307,23 +54359,23 @@
       </c>
     </row>
     <row r="464" ht="14.25">
-      <c r="X464" s="32"/>
+      <c r="X464" s="35"/>
       <c r="Y464" s="13"/>
       <c r="Z464" s="13"/>
       <c r="AA464" s="13"/>
-      <c r="AB464" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC464" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD464" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE464" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF464" s="29">
+      <c r="AB464" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC464" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD464" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE464" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF464" s="32">
         <v>1</v>
       </c>
       <c r="AI464" t="s">
@@ -54334,23 +54386,23 @@
       </c>
     </row>
     <row r="465" ht="14.25">
-      <c r="X465" s="32"/>
+      <c r="X465" s="35"/>
       <c r="Y465" s="13"/>
       <c r="Z465" s="13"/>
       <c r="AA465" s="13"/>
-      <c r="AB465" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC465" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD465" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE465" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF465" s="29">
+      <c r="AB465" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC465" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD465" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE465" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF465" s="32">
         <v>0</v>
       </c>
       <c r="AI465" t="s">
@@ -54361,23 +54413,23 @@
       </c>
     </row>
     <row r="466" ht="14.25">
-      <c r="X466" s="32"/>
+      <c r="X466" s="35"/>
       <c r="Y466" s="13"/>
       <c r="Z466" s="13"/>
       <c r="AA466" s="13"/>
-      <c r="AB466" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC466" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD466" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE466" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF466" s="29">
+      <c r="AB466" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC466" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD466" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE466" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF466" s="32">
         <v>1</v>
       </c>
       <c r="AI466" t="s">
@@ -54401,52 +54453,52 @@
       </c>
     </row>
     <row r="470" ht="14.25">
-      <c r="AB470" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="AC470" s="29"/>
-      <c r="AD470" s="29"/>
-      <c r="AE470" s="29"/>
-      <c r="AF470" s="29"/>
+      <c r="AB470" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="AC470" s="32"/>
+      <c r="AD470" s="32"/>
+      <c r="AE470" s="32"/>
+      <c r="AF470" s="32"/>
       <c r="AI470" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="471" ht="14.25">
-      <c r="X471" s="32"/>
+      <c r="X471" s="35"/>
       <c r="Y471" s="13"/>
       <c r="Z471" s="13"/>
       <c r="AA471" s="13"/>
-      <c r="AB471" s="29">
-        <v>1</v>
-      </c>
-      <c r="AC471" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD471" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE471" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF471" s="29">
+      <c r="AB471" s="32">
+        <v>1</v>
+      </c>
+      <c r="AC471" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD471" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE471" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF471" s="32">
         <v>0</v>
       </c>
       <c r="AI471" t="s">
         <v>136</v>
       </c>
       <c r="AJ471" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="484" ht="14.25">
       <c r="AH484" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="487" ht="14.25">
       <c r="A487" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B487" s="12"/>
       <c r="C487" s="12"/>
@@ -54465,7 +54517,7 @@
       <c r="L487" s="9"/>
       <c r="M487" s="9"/>
       <c r="N487" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="O487" s="12"/>
       <c r="P487" s="12"/>
@@ -54478,21 +54530,21 @@
       <c r="U487" s="11"/>
       <c r="V487" s="11"/>
       <c r="W487" s="11"/>
-      <c r="X487" s="32" t="s">
-        <v>210</v>
+      <c r="X487" s="35" t="s">
+        <v>214</v>
       </c>
       <c r="Y487" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Z487" s="12"/>
       <c r="AA487" s="12"/>
-      <c r="AB487" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC487" s="29"/>
-      <c r="AD487" s="29"/>
-      <c r="AE487" s="29"/>
-      <c r="AF487" s="29"/>
+      <c r="AB487" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC487" s="32"/>
+      <c r="AD487" s="32"/>
+      <c r="AE487" s="32"/>
+      <c r="AF487" s="32"/>
     </row>
     <row r="488" ht="14.25">
       <c r="A488" s="5"/>
@@ -54504,7 +54556,7 @@
       <c r="G488" s="7"/>
       <c r="H488" s="7"/>
       <c r="I488" s="12" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="J488" s="12"/>
       <c r="K488" s="12"/>
@@ -54520,7 +54572,7 @@
       <c r="U488" s="12"/>
       <c r="V488" s="12"/>
       <c r="W488" s="12"/>
-      <c r="X488" s="32" t="s">
+      <c r="X488" s="35" t="s">
         <v>71</v>
       </c>
       <c r="Y488" s="8" t="s">
@@ -54529,7 +54581,7 @@
       <c r="Z488" s="8"/>
       <c r="AA488" s="8"/>
       <c r="AB488" s="12" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AC488" s="12"/>
       <c r="AD488" s="12"/>
@@ -54539,7 +54591,7 @@
         <v>71</v>
       </c>
       <c r="AI488" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="489" ht="14.25">
@@ -54566,7 +54618,7 @@
       <c r="U489" s="12"/>
       <c r="V489" s="12"/>
       <c r="W489" s="12"/>
-      <c r="X489" s="32">
+      <c r="X489" s="35">
         <v>1</v>
       </c>
       <c r="Y489" s="8" t="s">
@@ -55246,7 +55298,7 @@
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
       <c r="V6" s="12" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="W6" s="12"/>
       <c r="X6" s="12"/>
@@ -55261,7 +55313,7 @@
     </row>
     <row r="7" ht="14.25">
       <c r="A7" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -55292,7 +55344,7 @@
       <c r="T7" s="11"/>
       <c r="U7" s="11"/>
       <c r="V7" s="12" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="W7" s="12"/>
       <c r="X7" s="12"/>
@@ -55347,7 +55399,7 @@
       <c r="P9" s="10"/>
       <c r="Q9" s="10"/>
       <c r="R9" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
@@ -55375,7 +55427,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="O10" s="12"/>
       <c r="P10" s="12"/>
@@ -55409,7 +55461,7 @@
     </row>
     <row r="13" ht="14.25">
       <c r="A13" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -55428,7 +55480,7 @@
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
       <c r="N13" s="12" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
@@ -55451,7 +55503,7 @@
     </row>
     <row r="14" ht="14.25">
       <c r="A14" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -55476,7 +55528,7 @@
       <c r="P14" s="10"/>
       <c r="Q14" s="10"/>
       <c r="R14" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="S14" s="12"/>
       <c r="T14" s="12"/>
@@ -55495,12 +55547,12 @@
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
       <c r="D16" s="7" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -55508,7 +55560,7 @@
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
       <c r="J16" s="12" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K16" s="12"/>
       <c r="L16" s="12"/>
@@ -55520,7 +55572,7 @@
       <c r="P16" s="10"/>
       <c r="Q16" s="10"/>
       <c r="R16" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="S16" s="12"/>
       <c r="T16" s="12"/>
@@ -55539,12 +55591,12 @@
     </row>
     <row r="17" ht="14.25">
       <c r="A17" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="7" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -55558,13 +55610,13 @@
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
       <c r="N17" s="12" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="O17" s="12"/>
       <c r="P17" s="12"/>
       <c r="Q17" s="12"/>
       <c r="R17" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="S17" s="12"/>
       <c r="T17" s="12"/>
@@ -55583,7 +55635,7 @@
     </row>
     <row r="19" ht="14.25">
       <c r="A19" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -55614,7 +55666,7 @@
       <c r="T19" s="11"/>
       <c r="U19" s="11"/>
       <c r="V19" s="12" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="W19" s="12"/>
       <c r="X19" s="12"/>
@@ -55659,29 +55711,29 @@
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
       <c r="V20" s="8" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="W20" s="8"/>
       <c r="X20" s="8"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
       <c r="AA20" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="AB20" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC20" s="29"/>
-      <c r="AD20" s="29"/>
-      <c r="AE20" s="29"/>
-      <c r="AF20" s="29"/>
+        <v>291</v>
+      </c>
+      <c r="AB20" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="32"/>
+      <c r="AE20" s="32"/>
+      <c r="AF20" s="32"/>
       <c r="AG20" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" ht="14.25">
       <c r="A22" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -55713,21 +55765,21 @@
     </row>
     <row r="23" ht="14.25">
       <c r="Y23" s="14" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Z23" s="14"/>
       <c r="AA23" s="14"/>
-      <c r="AB23" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC23" s="29"/>
-      <c r="AD23" s="29"/>
-      <c r="AE23" s="29"/>
-      <c r="AF23" s="29"/>
+      <c r="AB23" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC23" s="32"/>
+      <c r="AD23" s="32"/>
+      <c r="AE23" s="32"/>
+      <c r="AF23" s="32"/>
     </row>
     <row r="24" ht="14.25">
       <c r="X24" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Y24" s="6">
         <v>0</v>
@@ -55746,7 +55798,7 @@
     </row>
     <row r="25" ht="14.25">
       <c r="X25" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Y25" s="6">
         <v>0</v>
@@ -55765,7 +55817,7 @@
     </row>
     <row r="26" ht="14.25">
       <c r="X26" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Y26" s="6">
         <v>0</v>
@@ -55784,7 +55836,7 @@
     </row>
     <row r="27" ht="14.25">
       <c r="X27" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Y27" s="6">
         <v>0</v>
@@ -55803,7 +55855,7 @@
     </row>
     <row r="28" ht="14.25">
       <c r="X28" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Y28" s="6">
         <v>1</v>
@@ -55822,7 +55874,7 @@
     </row>
     <row r="29" ht="14.25">
       <c r="X29" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Y29" s="6">
         <v>1</v>
@@ -55875,42 +55927,42 @@
       <c r="AB32" s="6">
         <v>0</v>
       </c>
-      <c r="AC32" s="27">
+      <c r="AC32" s="29">
         <v>0</v>
       </c>
       <c r="AD32" t="s">
         <v>135</v>
       </c>
-      <c r="AE32" s="30" t="s">
-        <v>211</v>
+      <c r="AE32" s="33" t="s">
+        <v>215</v>
       </c>
       <c r="AF32" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" ht="14.25">
       <c r="AB33" s="6">
         <v>0</v>
       </c>
-      <c r="AC33" s="27">
+      <c r="AC33" s="29">
         <v>1</v>
       </c>
       <c r="AD33" t="s">
-        <v>213</v>
-      </c>
-      <c r="AE33" s="30"/>
+        <v>217</v>
+      </c>
+      <c r="AE33" s="33"/>
     </row>
     <row r="34" ht="14.25">
       <c r="AB34" s="6">
         <v>0</v>
       </c>
-      <c r="AC34" s="27">
+      <c r="AC34" s="29">
         <v>2</v>
       </c>
       <c r="AD34" t="s">
-        <v>215</v>
-      </c>
-      <c r="AE34" s="30"/>
+        <v>219</v>
+      </c>
+      <c r="AE34" s="33"/>
     </row>
     <row r="35" ht="14.25">
       <c r="U35" s="8" t="s">
@@ -55922,17 +55974,17 @@
       <c r="AB35" s="6">
         <v>0</v>
       </c>
-      <c r="AC35" s="27">
+      <c r="AC35" s="29">
         <v>3</v>
       </c>
       <c r="AD35" t="s">
-        <v>216</v>
-      </c>
-      <c r="AE35" s="30"/>
+        <v>220</v>
+      </c>
+      <c r="AE35" s="33"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="V36" s="30" t="s">
-        <v>289</v>
+      <c r="V36" s="33" t="s">
+        <v>293</v>
       </c>
       <c r="W36" s="6">
         <v>0</v>
@@ -55941,12 +55993,12 @@
         <v>0</v>
       </c>
       <c r="Y36" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AB36" s="6">
         <v>0</v>
       </c>
-      <c r="AC36" s="27">
+      <c r="AC36" s="29">
         <v>4</v>
       </c>
       <c r="AD36" t="s">
@@ -55954,7 +56006,7 @@
       </c>
     </row>
     <row r="37" ht="14.25">
-      <c r="V37" s="30"/>
+      <c r="V37" s="33"/>
       <c r="W37" s="6">
         <v>0</v>
       </c>
@@ -55962,12 +56014,12 @@
         <v>1</v>
       </c>
       <c r="Y37" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="AB37" s="6">
         <v>0</v>
       </c>
-      <c r="AC37" s="27">
+      <c r="AC37" s="29">
         <v>5</v>
       </c>
       <c r="AD37" t="s">
@@ -55975,7 +56027,7 @@
       </c>
     </row>
     <row r="38" ht="14.25">
-      <c r="V38" s="30"/>
+      <c r="V38" s="33"/>
       <c r="W38" s="6">
         <v>1</v>
       </c>
@@ -55983,12 +56035,12 @@
         <v>0</v>
       </c>
       <c r="Y38" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AB38" s="6">
         <v>0</v>
       </c>
-      <c r="AC38" s="27">
+      <c r="AC38" s="29">
         <v>6</v>
       </c>
       <c r="AD38" t="s">
@@ -55996,7 +56048,7 @@
       </c>
     </row>
     <row r="39" ht="14.25">
-      <c r="V39" s="30"/>
+      <c r="V39" s="33"/>
       <c r="W39" s="6">
         <v>1</v>
       </c>
@@ -56004,12 +56056,12 @@
         <v>1</v>
       </c>
       <c r="Y39" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AB39" s="6">
         <v>0</v>
       </c>
-      <c r="AC39" s="27">
+      <c r="AC39" s="29">
         <v>7</v>
       </c>
       <c r="AD39" t="s">
@@ -56018,14 +56070,14 @@
     </row>
     <row r="40" ht="14.25">
       <c r="V40" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="W40" s="6"/>
       <c r="X40" s="6"/>
       <c r="AB40" s="6">
         <v>0</v>
       </c>
-      <c r="AC40" s="27">
+      <c r="AC40" s="29">
         <v>8</v>
       </c>
       <c r="AD40" t="s">
@@ -56038,11 +56090,11 @@
       <c r="AB41" s="6">
         <v>0</v>
       </c>
-      <c r="AC41" s="27">
+      <c r="AC41" s="29">
         <v>9</v>
       </c>
       <c r="AD41" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" ht="14.25">
@@ -56051,11 +56103,11 @@
       <c r="AB42" s="6">
         <v>0</v>
       </c>
-      <c r="AC42" s="27" t="s">
-        <v>219</v>
+      <c r="AC42" s="29" t="s">
+        <v>223</v>
       </c>
       <c r="AD42" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" ht="14.25">
@@ -56064,56 +56116,56 @@
       <c r="AB43" s="6">
         <v>0</v>
       </c>
-      <c r="AC43" s="27" t="s">
-        <v>221</v>
+      <c r="AC43" s="29" t="s">
+        <v>225</v>
       </c>
       <c r="AD43" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="44" ht="14.25">
       <c r="AB44" s="6">
         <v>0</v>
       </c>
-      <c r="AC44" s="27" t="s">
-        <v>223</v>
+      <c r="AC44" s="29" t="s">
+        <v>227</v>
       </c>
       <c r="AD44" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" ht="14.25">
       <c r="AB45" s="6">
         <v>0</v>
       </c>
-      <c r="AC45" s="27" t="s">
-        <v>225</v>
+      <c r="AC45" s="29" t="s">
+        <v>229</v>
       </c>
       <c r="AD45" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" ht="14.25">
       <c r="AB46" s="6">
         <v>0</v>
       </c>
-      <c r="AC46" s="27" t="s">
-        <v>227</v>
+      <c r="AC46" s="29" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="47" ht="14.25">
       <c r="AB47" s="6">
         <v>0</v>
       </c>
-      <c r="AC47" s="27" t="s">
-        <v>230</v>
+      <c r="AC47" s="29" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="48" ht="14.25">
       <c r="AB48" s="6">
         <v>1</v>
       </c>
-      <c r="AC48" s="27">
+      <c r="AC48" s="29">
         <v>0</v>
       </c>
     </row>
@@ -56121,7 +56173,7 @@
       <c r="AB49" s="6">
         <v>1</v>
       </c>
-      <c r="AC49" s="27">
+      <c r="AC49" s="29">
         <v>1</v>
       </c>
     </row>
@@ -56129,7 +56181,7 @@
       <c r="AB50" s="6">
         <v>1</v>
       </c>
-      <c r="AC50" s="27">
+      <c r="AC50" s="29">
         <v>2</v>
       </c>
     </row>
@@ -56137,7 +56189,7 @@
       <c r="AB51" s="6">
         <v>1</v>
       </c>
-      <c r="AC51" s="27">
+      <c r="AC51" s="29">
         <v>3</v>
       </c>
     </row>
@@ -56145,7 +56197,7 @@
       <c r="AB52" s="6">
         <v>1</v>
       </c>
-      <c r="AC52" s="27">
+      <c r="AC52" s="29">
         <v>4</v>
       </c>
     </row>
@@ -56153,7 +56205,7 @@
       <c r="AB53" s="6">
         <v>1</v>
       </c>
-      <c r="AC53" s="27">
+      <c r="AC53" s="29">
         <v>5</v>
       </c>
     </row>
@@ -56161,7 +56213,7 @@
       <c r="AB54" s="6">
         <v>1</v>
       </c>
-      <c r="AC54" s="27">
+      <c r="AC54" s="29">
         <v>6</v>
       </c>
     </row>
@@ -56169,7 +56221,7 @@
       <c r="AB55" s="6">
         <v>1</v>
       </c>
-      <c r="AC55" s="27">
+      <c r="AC55" s="29">
         <v>7</v>
       </c>
     </row>
@@ -56177,7 +56229,7 @@
       <c r="AB56" s="6">
         <v>1</v>
       </c>
-      <c r="AC56" s="27">
+      <c r="AC56" s="29">
         <v>8</v>
       </c>
     </row>
@@ -56185,7 +56237,7 @@
       <c r="AB57" s="6">
         <v>1</v>
       </c>
-      <c r="AC57" s="27">
+      <c r="AC57" s="29">
         <v>9</v>
       </c>
     </row>
@@ -56193,43 +56245,43 @@
       <c r="AB58" s="6">
         <v>1</v>
       </c>
-      <c r="AC58" s="27" t="s">
-        <v>219</v>
+      <c r="AC58" s="29" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="59" ht="14.25">
       <c r="AB59" s="6">
         <v>1</v>
       </c>
-      <c r="AC59" s="27" t="s">
-        <v>221</v>
+      <c r="AC59" s="29" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="60" ht="14.25">
       <c r="AB60" s="6">
         <v>1</v>
       </c>
-      <c r="AC60" s="27" t="s">
-        <v>223</v>
+      <c r="AC60" s="29" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="61" ht="14.25">
       <c r="L61" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AB61" s="6">
         <v>1</v>
       </c>
-      <c r="AC61" s="27" t="s">
-        <v>225</v>
+      <c r="AC61" s="29" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="62" ht="14.25">
       <c r="AB62" s="6">
         <v>1</v>
       </c>
-      <c r="AC62" s="27" t="s">
-        <v>227</v>
+      <c r="AC62" s="29" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="63" ht="14.25">
@@ -56237,18 +56289,18 @@
         <v>9</v>
       </c>
       <c r="F63" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AB63" s="6">
         <v>1</v>
       </c>
-      <c r="AC63" s="27" t="s">
-        <v>230</v>
+      <c r="AC63" s="29" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="64" ht="14.25">
       <c r="A64" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
@@ -56284,26 +56336,26 @@
       <c r="W64" s="8"/>
       <c r="X64" s="8"/>
       <c r="Y64" s="14" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Z64" s="14"/>
       <c r="AA64" s="14"/>
-      <c r="AB64" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC64" s="29"/>
-      <c r="AD64" s="29"/>
-      <c r="AE64" s="29"/>
-      <c r="AF64" s="29"/>
+      <c r="AB64" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC64" s="32"/>
+      <c r="AD64" s="32"/>
+      <c r="AE64" s="32"/>
+      <c r="AF64" s="32"/>
     </row>
     <row r="65" ht="14.25">
       <c r="A65" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
       <c r="D65" s="7" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E65" s="7"/>
       <c r="F65" s="7"/>
@@ -56334,26 +56386,26 @@
       <c r="W65" s="8"/>
       <c r="X65" s="8"/>
       <c r="Y65" s="14" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Z65" s="14"/>
       <c r="AA65" s="14"/>
-      <c r="AB65" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC65" s="29"/>
-      <c r="AD65" s="29"/>
-      <c r="AE65" s="29"/>
-      <c r="AF65" s="29"/>
+      <c r="AB65" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC65" s="32"/>
+      <c r="AD65" s="32"/>
+      <c r="AE65" s="32"/>
+      <c r="AF65" s="32"/>
     </row>
     <row r="66" ht="14.25">
       <c r="A66" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
       <c r="D66" s="7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E66" s="7"/>
       <c r="F66" s="7"/>
@@ -56390,20 +56442,20 @@
       <c r="AA66" s="13"/>
       <c r="AB66" s="13"/>
       <c r="AC66" s="13"/>
-      <c r="AD66" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="AE66" s="32"/>
-      <c r="AF66" s="32"/>
+      <c r="AD66" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="AE66" s="35"/>
+      <c r="AF66" s="35"/>
     </row>
     <row r="67" ht="14.25">
       <c r="A67" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
       <c r="D67" s="7" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E67" s="7"/>
       <c r="F67" s="7"/>
@@ -56430,7 +56482,7 @@
     </row>
     <row r="68" ht="14.25">
       <c r="A68" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
@@ -56448,7 +56500,7 @@
       <c r="K68" s="9"/>
       <c r="L68" s="9"/>
       <c r="M68" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="N68" s="12"/>
       <c r="O68" s="12"/>
@@ -56464,7 +56516,7 @@
       <c r="W68" s="8"/>
       <c r="X68" s="8"/>
       <c r="Y68" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Z68" s="12"/>
       <c r="AA68" s="12"/>
@@ -56476,7 +56528,7 @@
     </row>
     <row r="69" ht="14.25">
       <c r="A69" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
@@ -56494,7 +56546,7 @@
       <c r="K69" s="9"/>
       <c r="L69" s="9"/>
       <c r="M69" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="N69" s="12"/>
       <c r="O69" s="12"/>
@@ -56510,7 +56562,7 @@
       <c r="W69" s="8"/>
       <c r="X69" s="8"/>
       <c r="Y69" s="12" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Z69" s="12"/>
       <c r="AA69" s="12"/>
@@ -56522,12 +56574,12 @@
     </row>
     <row r="70" ht="14.25">
       <c r="A70" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
       <c r="D70" s="7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7"/>
@@ -56540,7 +56592,7 @@
       <c r="K70" s="9"/>
       <c r="L70" s="9"/>
       <c r="M70" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="N70" s="12"/>
       <c r="O70" s="12"/>
@@ -56552,7 +56604,7 @@
       <c r="S70" s="11"/>
       <c r="T70" s="11"/>
       <c r="U70" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="V70" s="12"/>
       <c r="W70" s="12"/>
@@ -56568,19 +56620,19 @@
     </row>
     <row r="71" ht="14.25">
       <c r="A71" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
       <c r="D71" s="7" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E71" s="7"/>
       <c r="F71" s="7"/>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
       <c r="I71" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="J71" s="12"/>
       <c r="K71" s="12"/>
@@ -56598,7 +56650,7 @@
       <c r="S71" s="11"/>
       <c r="T71" s="11"/>
       <c r="U71" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="V71" s="12"/>
       <c r="W71" s="12"/>
@@ -56614,7 +56666,7 @@
     </row>
     <row r="72" ht="14.25">
       <c r="A72" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
@@ -56632,7 +56684,7 @@
       <c r="K72" s="9"/>
       <c r="L72" s="9"/>
       <c r="M72" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="N72" s="12"/>
       <c r="O72" s="12"/>
@@ -56644,7 +56696,7 @@
       <c r="S72" s="11"/>
       <c r="T72" s="11"/>
       <c r="U72" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="V72" s="12"/>
       <c r="W72" s="12"/>
@@ -56652,17 +56704,17 @@
       <c r="Y72" s="12"/>
       <c r="Z72" s="12"/>
       <c r="AA72" s="12"/>
-      <c r="AB72" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC72" s="29"/>
-      <c r="AD72" s="29"/>
-      <c r="AE72" s="29"/>
-      <c r="AF72" s="29"/>
+      <c r="AB72" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC72" s="32"/>
+      <c r="AD72" s="32"/>
+      <c r="AE72" s="32"/>
+      <c r="AF72" s="32"/>
     </row>
     <row r="74" ht="14.25">
       <c r="Q74" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="R74" s="12"/>
       <c r="S74" s="12"/>
@@ -56682,7 +56734,7 @@
     </row>
     <row r="76" ht="14.25">
       <c r="A76" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
@@ -56707,7 +56759,7 @@
       <c r="P76" s="10"/>
       <c r="Q76" s="10"/>
       <c r="R76" s="12" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="S76" s="12"/>
       <c r="T76" s="12"/>
@@ -56731,7 +56783,7 @@
     </row>
     <row r="84" ht="14.25">
       <c r="F84" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="85" ht="14.25">
@@ -56762,7 +56814,7 @@
         <v>9</v>
       </c>
       <c r="E97" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="98" ht="14.25">
@@ -56908,12 +56960,12 @@
     </row>
     <row r="100" ht="14.25">
       <c r="A100" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
       <c r="D100" s="7" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E100" s="7"/>
       <c r="F100" s="7"/>
@@ -56940,30 +56992,30 @@
       <c r="U100" s="11"/>
       <c r="V100" s="11"/>
       <c r="W100" s="11"/>
-      <c r="X100" s="32" t="s">
-        <v>210</v>
+      <c r="X100" s="35" t="s">
+        <v>214</v>
       </c>
       <c r="Y100" s="8" t="s">
         <v>7</v>
       </c>
       <c r="Z100" s="8"/>
       <c r="AA100" s="8"/>
-      <c r="AB100" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC100" s="29"/>
-      <c r="AD100" s="29"/>
-      <c r="AE100" s="29"/>
-      <c r="AF100" s="29"/>
+      <c r="AB100" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC100" s="32"/>
+      <c r="AD100" s="32"/>
+      <c r="AE100" s="32"/>
+      <c r="AF100" s="32"/>
     </row>
     <row r="101" ht="14.25">
       <c r="A101" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
       <c r="D101" s="7" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E101" s="7"/>
       <c r="F101" s="7"/>
@@ -56990,30 +57042,30 @@
       <c r="U101" s="11"/>
       <c r="V101" s="11"/>
       <c r="W101" s="11"/>
-      <c r="X101" s="32" t="s">
-        <v>210</v>
+      <c r="X101" s="35" t="s">
+        <v>214</v>
       </c>
       <c r="Y101" s="8" t="s">
         <v>7</v>
       </c>
       <c r="Z101" s="8"/>
       <c r="AA101" s="8"/>
-      <c r="AB101" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC101" s="29"/>
-      <c r="AD101" s="29"/>
-      <c r="AE101" s="29"/>
-      <c r="AF101" s="29"/>
+      <c r="AB101" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC101" s="32"/>
+      <c r="AD101" s="32"/>
+      <c r="AE101" s="32"/>
+      <c r="AF101" s="32"/>
     </row>
     <row r="102" ht="14.25">
       <c r="A102" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
       <c r="D102" s="7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E102" s="7"/>
       <c r="F102" s="7"/>
@@ -57046,22 +57098,22 @@
       </c>
       <c r="Z102" s="8"/>
       <c r="AA102" s="8"/>
-      <c r="AB102" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC102" s="29"/>
-      <c r="AD102" s="29"/>
-      <c r="AE102" s="29"/>
-      <c r="AF102" s="29"/>
+      <c r="AB102" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC102" s="32"/>
+      <c r="AD102" s="32"/>
+      <c r="AE102" s="32"/>
+      <c r="AF102" s="32"/>
     </row>
     <row r="103" ht="14.25">
       <c r="A103" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
       <c r="D103" s="7" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E103" s="7"/>
       <c r="F103" s="7"/>
@@ -57094,17 +57146,17 @@
       </c>
       <c r="Z103" s="8"/>
       <c r="AA103" s="8"/>
-      <c r="AB103" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC103" s="29"/>
-      <c r="AD103" s="29"/>
-      <c r="AE103" s="29"/>
-      <c r="AF103" s="29"/>
+      <c r="AB103" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC103" s="32"/>
+      <c r="AD103" s="32"/>
+      <c r="AE103" s="32"/>
+      <c r="AF103" s="32"/>
     </row>
     <row r="104" ht="14.25">
       <c r="A104" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B104" s="12"/>
       <c r="C104" s="12"/>
@@ -57150,7 +57202,7 @@
     </row>
     <row r="105" ht="14.25">
       <c r="A105" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B105" s="12"/>
       <c r="C105" s="12"/>
@@ -57196,12 +57248,12 @@
     </row>
     <row r="106" ht="14.25">
       <c r="A106" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
       <c r="D106" s="7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E106" s="7"/>
       <c r="F106" s="7"/>
@@ -57215,7 +57267,7 @@
       <c r="L106" s="9"/>
       <c r="M106" s="9"/>
       <c r="N106" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="O106" s="12"/>
       <c r="P106" s="12"/>
@@ -57229,7 +57281,7 @@
       <c r="V106" s="11"/>
       <c r="W106" s="11"/>
       <c r="X106" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Y106" s="12"/>
       <c r="Z106" s="12"/>
@@ -57242,19 +57294,19 @@
     </row>
     <row r="107" ht="14.25">
       <c r="A107" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
       <c r="D107" s="7" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E107" s="7"/>
       <c r="F107" s="7"/>
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
       <c r="I107" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="J107" s="12"/>
       <c r="K107" s="12"/>
@@ -57275,7 +57327,7 @@
       <c r="V107" s="11"/>
       <c r="W107" s="11"/>
       <c r="X107" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Y107" s="12"/>
       <c r="Z107" s="12"/>
@@ -57288,7 +57340,7 @@
     </row>
     <row r="108" ht="14.25">
       <c r="A108" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
@@ -57307,7 +57359,7 @@
       <c r="L108" s="9"/>
       <c r="M108" s="9"/>
       <c r="N108" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="O108" s="12"/>
       <c r="P108" s="12"/>
@@ -57320,21 +57372,21 @@
       <c r="U108" s="11"/>
       <c r="V108" s="11"/>
       <c r="W108" s="11"/>
-      <c r="X108" s="32" t="s">
-        <v>210</v>
+      <c r="X108" s="35" t="s">
+        <v>214</v>
       </c>
       <c r="Y108" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Z108" s="12"/>
       <c r="AA108" s="12"/>
-      <c r="AB108" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC108" s="29"/>
-      <c r="AD108" s="29"/>
-      <c r="AE108" s="29"/>
-      <c r="AF108" s="29"/>
+      <c r="AB108" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC108" s="32"/>
+      <c r="AD108" s="32"/>
+      <c r="AE108" s="32"/>
+      <c r="AF108" s="32"/>
     </row>
     <row r="109" ht="14.25">
       <c r="A109" s="6">
@@ -57436,12 +57488,12 @@
     </row>
     <row r="110" ht="14.25">
       <c r="A110" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
       <c r="D110" s="7" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E110" s="7"/>
       <c r="F110" s="7"/>
@@ -57468,26 +57520,26 @@
       <c r="U110" s="11"/>
       <c r="V110" s="11"/>
       <c r="W110" s="11"/>
-      <c r="X110" s="32" t="s">
-        <v>210</v>
+      <c r="X110" s="35" t="s">
+        <v>214</v>
       </c>
       <c r="Y110" s="8" t="s">
         <v>7</v>
       </c>
       <c r="Z110" s="8"/>
       <c r="AA110" s="8"/>
-      <c r="AB110" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC110" s="29"/>
-      <c r="AD110" s="29"/>
-      <c r="AE110" s="29"/>
-      <c r="AF110" s="29"/>
+      <c r="AB110" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC110" s="32"/>
+      <c r="AD110" s="32"/>
+      <c r="AE110" s="32"/>
+      <c r="AF110" s="32"/>
       <c r="AG110" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="AH110" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AQ110" t="s">
         <v>76</v>
@@ -57527,25 +57579,25 @@
       <c r="U111" s="5"/>
       <c r="V111" s="5"/>
       <c r="W111" s="5"/>
-      <c r="X111" s="29">
+      <c r="X111" s="32">
         <v>0</v>
       </c>
       <c r="Y111" s="5"/>
       <c r="Z111" s="5"/>
       <c r="AA111" s="5"/>
-      <c r="AB111" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC111" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD111" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE111" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF111" s="29">
+      <c r="AB111" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="32">
         <v>0</v>
       </c>
       <c r="AG111" s="5">
@@ -57554,11 +57606,11 @@
       <c r="AH111" t="s">
         <v>135</v>
       </c>
-      <c r="AI111" s="33" t="s">
-        <v>211</v>
+      <c r="AI111" s="36" t="s">
+        <v>215</v>
       </c>
       <c r="AJ111" s="6" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="AK111" s="6"/>
       <c r="AL111" s="6"/>
@@ -57590,34 +57642,34 @@
       <c r="U112" s="5"/>
       <c r="V112" s="5"/>
       <c r="W112" s="5"/>
-      <c r="X112" s="29">
+      <c r="X112" s="32">
         <v>0</v>
       </c>
       <c r="Y112" s="5"/>
       <c r="Z112" s="5"/>
       <c r="AA112" s="5"/>
-      <c r="AB112" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC112" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD112" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE112" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF112" s="29">
+      <c r="AB112" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC112" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD112" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE112" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF112" s="32">
         <v>1</v>
       </c>
       <c r="AG112" s="5">
         <v>1</v>
       </c>
       <c r="AH112" t="s">
-        <v>213</v>
-      </c>
-      <c r="AI112" s="33"/>
+        <v>217</v>
+      </c>
+      <c r="AI112" s="36"/>
       <c r="AJ112" s="6"/>
       <c r="AK112" s="6"/>
       <c r="AL112" s="6"/>
@@ -57649,34 +57701,34 @@
       <c r="U113" s="5"/>
       <c r="V113" s="5"/>
       <c r="W113" s="5"/>
-      <c r="X113" s="29">
+      <c r="X113" s="32">
         <v>0</v>
       </c>
       <c r="Y113" s="5"/>
       <c r="Z113" s="5"/>
       <c r="AA113" s="5"/>
-      <c r="AB113" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC113" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD113" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE113" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF113" s="29">
+      <c r="AB113" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC113" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD113" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE113" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF113" s="32">
         <v>0</v>
       </c>
       <c r="AG113" s="5">
         <v>2</v>
       </c>
       <c r="AH113" t="s">
-        <v>215</v>
-      </c>
-      <c r="AI113" s="33"/>
+        <v>219</v>
+      </c>
+      <c r="AI113" s="36"/>
       <c r="AJ113" s="6"/>
       <c r="AK113" s="6"/>
       <c r="AL113" s="6"/>
@@ -57708,34 +57760,34 @@
       <c r="U114" s="5"/>
       <c r="V114" s="5"/>
       <c r="W114" s="5"/>
-      <c r="X114" s="29">
+      <c r="X114" s="32">
         <v>0</v>
       </c>
       <c r="Y114" s="5"/>
       <c r="Z114" s="5"/>
       <c r="AA114" s="5"/>
-      <c r="AB114" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC114" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD114" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE114" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF114" s="29">
+      <c r="AB114" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC114" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD114" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE114" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF114" s="32">
         <v>1</v>
       </c>
       <c r="AG114" s="5">
         <v>3</v>
       </c>
       <c r="AH114" t="s">
-        <v>216</v>
-      </c>
-      <c r="AI114" s="33"/>
+        <v>220</v>
+      </c>
+      <c r="AI114" s="36"/>
       <c r="AJ114" s="6"/>
       <c r="AK114" s="6"/>
       <c r="AL114" s="6"/>
@@ -57767,25 +57819,25 @@
       <c r="U115" s="5"/>
       <c r="V115" s="5"/>
       <c r="W115" s="5"/>
-      <c r="X115" s="29">
+      <c r="X115" s="32">
         <v>0</v>
       </c>
       <c r="Y115" s="5"/>
       <c r="Z115" s="5"/>
       <c r="AA115" s="5"/>
-      <c r="AB115" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC115" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD115" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE115" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF115" s="29">
+      <c r="AB115" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC115" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD115" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE115" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF115" s="32">
         <v>0</v>
       </c>
       <c r="AG115" s="5">
@@ -57826,25 +57878,25 @@
       <c r="U116" s="5"/>
       <c r="V116" s="5"/>
       <c r="W116" s="5"/>
-      <c r="X116" s="29">
+      <c r="X116" s="32">
         <v>0</v>
       </c>
       <c r="Y116" s="5"/>
       <c r="Z116" s="5"/>
       <c r="AA116" s="5"/>
-      <c r="AB116" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC116" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD116" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE116" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF116" s="29">
+      <c r="AB116" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE116" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF116" s="32">
         <v>1</v>
       </c>
       <c r="AG116" s="5">
@@ -57882,25 +57934,25 @@
       <c r="U117" s="5"/>
       <c r="V117" s="5"/>
       <c r="W117" s="5"/>
-      <c r="X117" s="29">
+      <c r="X117" s="32">
         <v>0</v>
       </c>
       <c r="Y117" s="5"/>
       <c r="Z117" s="5"/>
       <c r="AA117" s="5"/>
-      <c r="AB117" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC117" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD117" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE117" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF117" s="29">
+      <c r="AB117" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC117" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD117" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE117" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF117" s="32">
         <v>0</v>
       </c>
       <c r="AG117" s="5">
@@ -57938,25 +57990,25 @@
       <c r="U118" s="5"/>
       <c r="V118" s="5"/>
       <c r="W118" s="5"/>
-      <c r="X118" s="29">
+      <c r="X118" s="32">
         <v>0</v>
       </c>
       <c r="Y118" s="5"/>
       <c r="Z118" s="5"/>
       <c r="AA118" s="5"/>
-      <c r="AB118" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC118" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD118" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE118" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF118" s="29">
+      <c r="AB118" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC118" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD118" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE118" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF118" s="32">
         <v>1</v>
       </c>
       <c r="AG118" s="5">
@@ -57994,25 +58046,25 @@
       <c r="U119" s="5"/>
       <c r="V119" s="5"/>
       <c r="W119" s="5"/>
-      <c r="X119" s="29">
+      <c r="X119" s="32">
         <v>0</v>
       </c>
       <c r="Y119" s="5"/>
       <c r="Z119" s="5"/>
       <c r="AA119" s="5"/>
-      <c r="AB119" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC119" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD119" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE119" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF119" s="29">
+      <c r="AB119" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC119" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD119" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE119" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF119" s="32">
         <v>0</v>
       </c>
       <c r="AG119" s="5">
@@ -58049,32 +58101,32 @@
       <c r="U120" s="5"/>
       <c r="V120" s="5"/>
       <c r="W120" s="5"/>
-      <c r="X120" s="29">
+      <c r="X120" s="32">
         <v>0</v>
       </c>
       <c r="Y120" s="5"/>
       <c r="Z120" s="5"/>
       <c r="AA120" s="5"/>
-      <c r="AB120" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC120" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD120" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE120" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF120" s="29">
+      <c r="AB120" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC120" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD120" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE120" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF120" s="32">
         <v>1</v>
       </c>
       <c r="AG120" s="5">
         <v>9</v>
       </c>
       <c r="AH120" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AI120" s="6"/>
       <c r="AJ120" s="6"/>
@@ -58105,29 +58157,29 @@
       <c r="U121" s="5"/>
       <c r="V121" s="5"/>
       <c r="W121" s="5"/>
-      <c r="X121" s="29">
+      <c r="X121" s="32">
         <v>0</v>
       </c>
       <c r="Y121" s="5"/>
       <c r="Z121" s="5"/>
       <c r="AA121" s="5"/>
-      <c r="AB121" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC121" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD121" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE121" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF121" s="29">
+      <c r="AB121" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC121" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD121" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE121" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF121" s="32">
         <v>0</v>
       </c>
       <c r="AG121" s="5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AI121" s="6"/>
       <c r="AJ121" s="6"/>
@@ -58158,32 +58210,32 @@
       <c r="U122" s="5"/>
       <c r="V122" s="5"/>
       <c r="W122" s="5"/>
-      <c r="X122" s="29">
+      <c r="X122" s="32">
         <v>0</v>
       </c>
       <c r="Y122" s="5"/>
       <c r="Z122" s="5"/>
       <c r="AA122" s="5"/>
-      <c r="AB122" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC122" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD122" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE122" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF122" s="29">
+      <c r="AB122" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC122" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD122" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE122" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF122" s="32">
         <v>1</v>
       </c>
       <c r="AG122" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AH122" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AJ122" s="6"/>
       <c r="AK122" s="6"/>
@@ -58213,32 +58265,32 @@
       <c r="U123" s="5"/>
       <c r="V123" s="5"/>
       <c r="W123" s="5"/>
-      <c r="X123" s="29">
+      <c r="X123" s="32">
         <v>0</v>
       </c>
       <c r="Y123" s="5"/>
       <c r="Z123" s="5"/>
       <c r="AA123" s="5"/>
-      <c r="AB123" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC123" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD123" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE123" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF123" s="29">
+      <c r="AB123" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC123" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD123" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE123" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF123" s="32">
         <v>0</v>
       </c>
       <c r="AG123" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AH123" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AJ123" s="6"/>
       <c r="AK123" s="6"/>
@@ -58268,29 +58320,29 @@
       <c r="U124" s="5"/>
       <c r="V124" s="5"/>
       <c r="W124" s="5"/>
-      <c r="X124" s="29">
+      <c r="X124" s="32">
         <v>0</v>
       </c>
       <c r="Y124" s="5"/>
       <c r="Z124" s="5"/>
       <c r="AA124" s="5"/>
-      <c r="AB124" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC124" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD124" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE124" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF124" s="29">
+      <c r="AB124" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC124" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD124" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE124" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF124" s="32">
         <v>1</v>
       </c>
       <c r="AG124" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AI124" s="6"/>
       <c r="AJ124" s="6"/>
@@ -58321,32 +58373,32 @@
       <c r="U125" s="5"/>
       <c r="V125" s="5"/>
       <c r="W125" s="5"/>
-      <c r="X125" s="29">
+      <c r="X125" s="32">
         <v>0</v>
       </c>
       <c r="Y125" s="5"/>
       <c r="Z125" s="5"/>
       <c r="AA125" s="5"/>
-      <c r="AB125" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC125" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD125" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE125" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF125" s="29">
+      <c r="AB125" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC125" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD125" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE125" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF125" s="32">
         <v>0</v>
       </c>
       <c r="AG125" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="AH125" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="AI125" s="6"/>
       <c r="AJ125" s="6"/>
@@ -58377,32 +58429,32 @@
       <c r="U126" s="5"/>
       <c r="V126" s="5"/>
       <c r="W126" s="5"/>
-      <c r="X126" s="29">
+      <c r="X126" s="32">
         <v>0</v>
       </c>
       <c r="Y126" s="5"/>
       <c r="Z126" s="5"/>
       <c r="AA126" s="5"/>
-      <c r="AB126" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC126" s="29">
-        <v>1</v>
-      </c>
-      <c r="AD126" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE126" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF126" s="29">
+      <c r="AB126" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC126" s="32">
+        <v>1</v>
+      </c>
+      <c r="AD126" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE126" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF126" s="32">
         <v>1</v>
       </c>
       <c r="AG126" s="5" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AH126" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="AI126" s="6"/>
       <c r="AJ126" s="6"/>
@@ -58433,19 +58485,19 @@
       <c r="U127" s="5"/>
       <c r="V127" s="5"/>
       <c r="W127" s="5"/>
-      <c r="X127" s="29">
+      <c r="X127" s="32">
         <v>1</v>
       </c>
       <c r="Y127" s="5"/>
       <c r="Z127" s="5"/>
       <c r="AA127" s="5"/>
-      <c r="AB127" s="29" t="s">
-        <v>259</v>
-      </c>
-      <c r="AC127" s="29"/>
-      <c r="AD127" s="29"/>
-      <c r="AE127" s="29"/>
-      <c r="AF127" s="29"/>
+      <c r="AB127" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="AC127" s="32"/>
+      <c r="AD127" s="32"/>
+      <c r="AE127" s="32"/>
+      <c r="AF127" s="32"/>
       <c r="AG127" s="5"/>
       <c r="AH127" s="6" t="s">
         <v>15</v>
@@ -58554,12 +58606,12 @@
     </row>
     <row r="129" ht="14.25">
       <c r="A129" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
       <c r="D129" s="7" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E129" s="7"/>
       <c r="F129" s="7"/>
@@ -58586,21 +58638,21 @@
       <c r="U129" s="11"/>
       <c r="V129" s="11"/>
       <c r="W129" s="11"/>
-      <c r="X129" s="32" t="s">
-        <v>210</v>
+      <c r="X129" s="35" t="s">
+        <v>214</v>
       </c>
       <c r="Y129" s="8" t="s">
         <v>7</v>
       </c>
       <c r="Z129" s="8"/>
       <c r="AA129" s="8"/>
-      <c r="AB129" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC129" s="29"/>
-      <c r="AD129" s="29"/>
-      <c r="AE129" s="29"/>
-      <c r="AF129" s="29"/>
+      <c r="AB129" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC129" s="32"/>
+      <c r="AD129" s="32"/>
+      <c r="AE129" s="32"/>
+      <c r="AF129" s="32"/>
     </row>
     <row r="130" ht="14.25">
       <c r="A130" s="6">
@@ -58702,12 +58754,12 @@
     </row>
     <row r="131" ht="14.25">
       <c r="A131" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B131" s="12"/>
       <c r="C131" s="12"/>
       <c r="D131" s="7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E131" s="7"/>
       <c r="F131" s="7"/>
@@ -58740,15 +58792,15 @@
       </c>
       <c r="Z131" s="8"/>
       <c r="AA131" s="8"/>
-      <c r="AB131" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC131" s="29"/>
-      <c r="AD131" s="29"/>
-      <c r="AE131" s="29"/>
-      <c r="AF131" s="29"/>
+      <c r="AB131" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC131" s="32"/>
+      <c r="AD131" s="32"/>
+      <c r="AE131" s="32"/>
+      <c r="AF131" s="32"/>
       <c r="AH131" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="132" ht="14.25">
@@ -58781,7 +58833,7 @@
       <c r="Q132" s="5"/>
       <c r="R132" s="5"/>
       <c r="S132" s="14" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="T132" s="14"/>
       <c r="U132" s="14"/>
@@ -58797,7 +58849,7 @@
       <c r="AE132" s="17"/>
       <c r="AF132" s="17"/>
       <c r="AH132" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="133" ht="14.25">
@@ -58900,12 +58952,12 @@
     </row>
     <row r="134" ht="14.25">
       <c r="A134" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
       <c r="D134" s="7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E134" s="7"/>
       <c r="F134" s="7"/>
@@ -58938,29 +58990,29 @@
       </c>
       <c r="Z134" s="8"/>
       <c r="AA134" s="8"/>
-      <c r="AB134" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC134" s="29"/>
-      <c r="AD134" s="29"/>
-      <c r="AE134" s="29"/>
-      <c r="AF134" s="29"/>
+      <c r="AB134" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC134" s="32"/>
+      <c r="AD134" s="32"/>
+      <c r="AE134" s="32"/>
+      <c r="AF134" s="32"/>
     </row>
     <row r="135" ht="14.25">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
       <c r="D135" s="7" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="G135" s="7" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="H135" s="7">
         <v>1</v>
@@ -58976,7 +59028,7 @@
       <c r="Q135" s="5"/>
       <c r="R135" s="5"/>
       <c r="S135" s="14" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="T135" s="14"/>
       <c r="U135" s="14"/>
@@ -59092,7 +59144,7 @@
     </row>
     <row r="137" ht="14.25">
       <c r="A137" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B137" s="12"/>
       <c r="C137" s="12"/>
@@ -59160,25 +59212,25 @@
       <c r="K138" s="5"/>
       <c r="L138" s="5"/>
       <c r="M138" s="5"/>
-      <c r="N138" s="28"/>
-      <c r="O138" s="28"/>
-      <c r="P138" s="28"/>
-      <c r="Q138" s="28"/>
-      <c r="R138" s="28"/>
-      <c r="S138" s="28"/>
-      <c r="T138" s="28"/>
-      <c r="U138" s="28"/>
-      <c r="V138" s="28"/>
-      <c r="W138" s="28"/>
-      <c r="X138" s="28"/>
+      <c r="N138" s="31"/>
+      <c r="O138" s="31"/>
+      <c r="P138" s="31"/>
+      <c r="Q138" s="31"/>
+      <c r="R138" s="31"/>
+      <c r="S138" s="31"/>
+      <c r="T138" s="31"/>
+      <c r="U138" s="31"/>
+      <c r="V138" s="31"/>
+      <c r="W138" s="31"/>
+      <c r="X138" s="31"/>
       <c r="Y138" s="5"/>
       <c r="Z138" s="5"/>
       <c r="AA138" s="5"/>
-      <c r="AB138" s="28"/>
-      <c r="AC138" s="28"/>
-      <c r="AD138" s="28"/>
-      <c r="AE138" s="28"/>
-      <c r="AF138" s="28"/>
+      <c r="AB138" s="31"/>
+      <c r="AC138" s="31"/>
+      <c r="AD138" s="31"/>
+      <c r="AE138" s="31"/>
+      <c r="AF138" s="31"/>
     </row>
     <row r="139" ht="14.25">
       <c r="A139" s="6">
@@ -59280,7 +59332,7 @@
     </row>
     <row r="140" ht="14.25">
       <c r="A140" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
@@ -59348,25 +59400,25 @@
       <c r="K141" s="5"/>
       <c r="L141" s="5"/>
       <c r="M141" s="5"/>
-      <c r="N141" s="28"/>
-      <c r="O141" s="28"/>
-      <c r="P141" s="28"/>
-      <c r="Q141" s="28"/>
-      <c r="R141" s="28"/>
-      <c r="S141" s="28"/>
-      <c r="T141" s="28"/>
-      <c r="U141" s="28"/>
-      <c r="V141" s="28"/>
-      <c r="W141" s="28"/>
-      <c r="X141" s="28"/>
+      <c r="N141" s="31"/>
+      <c r="O141" s="31"/>
+      <c r="P141" s="31"/>
+      <c r="Q141" s="31"/>
+      <c r="R141" s="31"/>
+      <c r="S141" s="31"/>
+      <c r="T141" s="31"/>
+      <c r="U141" s="31"/>
+      <c r="V141" s="31"/>
+      <c r="W141" s="31"/>
+      <c r="X141" s="31"/>
       <c r="Y141" s="5"/>
       <c r="Z141" s="5"/>
       <c r="AA141" s="5"/>
-      <c r="AB141" s="28"/>
-      <c r="AC141" s="28"/>
-      <c r="AD141" s="28"/>
-      <c r="AE141" s="28"/>
-      <c r="AF141" s="28"/>
+      <c r="AB141" s="31"/>
+      <c r="AC141" s="31"/>
+      <c r="AD141" s="31"/>
+      <c r="AE141" s="31"/>
+      <c r="AF141" s="31"/>
     </row>
     <row r="142" ht="14.25">
       <c r="A142" s="6">
@@ -59468,12 +59520,12 @@
     </row>
     <row r="143" ht="14.25">
       <c r="A143" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B143" s="12"/>
       <c r="C143" s="12"/>
       <c r="D143" s="7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E143" s="7"/>
       <c r="F143" s="7"/>
@@ -59487,7 +59539,7 @@
       <c r="L143" s="9"/>
       <c r="M143" s="9"/>
       <c r="N143" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="O143" s="12"/>
       <c r="P143" s="12"/>
@@ -59501,7 +59553,7 @@
       <c r="V143" s="11"/>
       <c r="W143" s="11"/>
       <c r="X143" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Y143" s="12"/>
       <c r="Z143" s="12"/>
@@ -59558,20 +59610,20 @@
     </row>
     <row r="145" ht="14.25">
       <c r="N145" s="12" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O145" s="12"/>
       <c r="P145" s="12" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q145" s="12"/>
       <c r="R145" s="12"/>
       <c r="X145" s="12" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Y145" s="12"/>
       <c r="Z145" s="12" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AA145" s="12"/>
       <c r="AB145" s="12"/>
@@ -59610,19 +59662,19 @@
     </row>
     <row r="148" ht="14.25">
       <c r="N148" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="O148" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="P148" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q148" t="s">
+        <v>274</v>
+      </c>
+      <c r="R148" t="s">
         <v>270</v>
-      </c>
-      <c r="R148" t="s">
-        <v>266</v>
       </c>
       <c r="Z148" t="s">
         <v>98</v>
@@ -59630,18 +59682,18 @@
     </row>
     <row r="149" ht="14.25">
       <c r="R149" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Z149" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="150" ht="14.25">
       <c r="R150" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="T150" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="152" ht="14.25">
@@ -59744,19 +59796,19 @@
     </row>
     <row r="153" ht="14.25">
       <c r="A153" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B153" s="12"/>
       <c r="C153" s="12"/>
       <c r="D153" s="7" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E153" s="7"/>
       <c r="F153" s="7"/>
       <c r="G153" s="7"/>
       <c r="H153" s="7"/>
       <c r="I153" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="J153" s="12"/>
       <c r="K153" s="12"/>
@@ -59777,7 +59829,7 @@
       <c r="V153" s="11"/>
       <c r="W153" s="11"/>
       <c r="X153" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Y153" s="12"/>
       <c r="Z153" s="12"/>
@@ -59834,11 +59886,11 @@
     </row>
     <row r="155" ht="14.25">
       <c r="I155" s="12" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J155" s="12"/>
       <c r="K155" s="12" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L155" s="12"/>
       <c r="M155" s="12"/>
@@ -59855,15 +59907,15 @@
     </row>
     <row r="157" ht="14.25">
       <c r="X157" s="12" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Y157" s="12"/>
       <c r="Z157" s="14" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AA157" s="14"/>
       <c r="AB157" s="12" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AC157" s="12"/>
       <c r="AD157" s="12"/>
@@ -59892,10 +59944,10 @@
       <c r="Y158" s="13">
         <v>0</v>
       </c>
-      <c r="Z158" s="28">
-        <v>0</v>
-      </c>
-      <c r="AA158" s="28">
+      <c r="Z158" s="31">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="31">
         <v>0</v>
       </c>
       <c r="AB158" t="s">
@@ -59916,14 +59968,14 @@
       <c r="Y159" s="13">
         <v>1</v>
       </c>
-      <c r="Z159" s="28">
-        <v>0</v>
-      </c>
-      <c r="AA159" s="28">
+      <c r="Z159" s="31">
+        <v>0</v>
+      </c>
+      <c r="AA159" s="31">
         <v>1</v>
       </c>
       <c r="AB159" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AC159" s="5"/>
       <c r="AD159" s="5"/>
@@ -59940,14 +59992,14 @@
       <c r="Y160" s="13">
         <v>0</v>
       </c>
-      <c r="Z160" s="28">
-        <v>1</v>
-      </c>
-      <c r="AA160" s="28">
+      <c r="Z160" s="31">
+        <v>1</v>
+      </c>
+      <c r="AA160" s="31">
         <v>0</v>
       </c>
       <c r="AB160" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="AC160" s="5"/>
       <c r="AD160" s="5"/>
@@ -59956,7 +60008,7 @@
     </row>
     <row r="161" ht="14.25">
       <c r="W161" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="X161" s="13">
         <v>1</v>
@@ -59964,14 +60016,14 @@
       <c r="Y161" s="13">
         <v>1</v>
       </c>
-      <c r="Z161" s="28">
-        <v>1</v>
-      </c>
-      <c r="AA161" s="28">
+      <c r="Z161" s="31">
+        <v>1</v>
+      </c>
+      <c r="AA161" s="31">
         <v>1</v>
       </c>
       <c r="AB161" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AC161" s="5"/>
       <c r="AD161" s="5"/>
@@ -60078,7 +60130,7 @@
     </row>
     <row r="165" ht="14.25">
       <c r="A165" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B165" s="12"/>
       <c r="C165" s="12"/>
@@ -60097,7 +60149,7 @@
       <c r="L165" s="9"/>
       <c r="M165" s="9"/>
       <c r="N165" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="O165" s="12"/>
       <c r="P165" s="12"/>
@@ -60110,21 +60162,21 @@
       <c r="U165" s="11"/>
       <c r="V165" s="11"/>
       <c r="W165" s="11"/>
-      <c r="X165" s="32" t="s">
-        <v>210</v>
+      <c r="X165" s="35" t="s">
+        <v>214</v>
       </c>
       <c r="Y165" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Z165" s="12"/>
       <c r="AA165" s="12"/>
-      <c r="AB165" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC165" s="29"/>
-      <c r="AD165" s="29"/>
-      <c r="AE165" s="29"/>
-      <c r="AF165" s="29"/>
+      <c r="AB165" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC165" s="32"/>
+      <c r="AD165" s="32"/>
+      <c r="AE165" s="32"/>
+      <c r="AF165" s="32"/>
     </row>
     <row r="166" ht="14.25">
       <c r="A166" s="5"/>
@@ -60162,17 +60214,17 @@
       <c r="U166" s="5"/>
       <c r="V166" s="5"/>
       <c r="W166" s="5"/>
-      <c r="X166" s="32"/>
+      <c r="X166" s="35"/>
       <c r="Y166" s="13"/>
       <c r="Z166" s="13"/>
       <c r="AA166" s="13"/>
-      <c r="AB166" s="29" t="s">
-        <v>277</v>
-      </c>
-      <c r="AC166" s="29"/>
-      <c r="AD166" s="29"/>
-      <c r="AE166" s="29"/>
-      <c r="AF166" s="29"/>
+      <c r="AB166" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="AC166" s="32"/>
+      <c r="AD166" s="32"/>
+      <c r="AE166" s="32"/>
+      <c r="AF166" s="32"/>
     </row>
     <row r="167" ht="14.25">
       <c r="A167" s="5"/>
@@ -60200,25 +60252,25 @@
       <c r="U167" s="5"/>
       <c r="V167" s="5"/>
       <c r="W167" s="5"/>
-      <c r="X167" s="32">
+      <c r="X167" s="35">
         <v>0</v>
       </c>
       <c r="Y167" s="13"/>
       <c r="Z167" s="13"/>
       <c r="AA167" s="13"/>
-      <c r="AB167" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC167" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD167" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE167" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF167" s="29">
+      <c r="AB167" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC167" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD167" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE167" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF167" s="32">
         <v>0</v>
       </c>
     </row>
@@ -60256,15 +60308,15 @@
       <c r="U168" s="5"/>
       <c r="V168" s="5"/>
       <c r="W168" s="5"/>
-      <c r="X168" s="32"/>
+      <c r="X168" s="35"/>
       <c r="Y168" s="13"/>
       <c r="Z168" s="13"/>
       <c r="AA168" s="13"/>
-      <c r="AB168" s="29"/>
-      <c r="AC168" s="29"/>
-      <c r="AD168" s="29"/>
-      <c r="AE168" s="29"/>
-      <c r="AF168" s="29"/>
+      <c r="AB168" s="32"/>
+      <c r="AC168" s="32"/>
+      <c r="AD168" s="32"/>
+      <c r="AE168" s="32"/>
+      <c r="AF168" s="32"/>
       <c r="AH168" t="s">
         <v>87</v>
       </c>
@@ -60303,15 +60355,15 @@
       <c r="U169" s="5"/>
       <c r="V169" s="5"/>
       <c r="W169" s="5"/>
-      <c r="X169" s="32"/>
+      <c r="X169" s="35"/>
       <c r="Y169" s="13"/>
       <c r="Z169" s="13"/>
       <c r="AA169" s="13"/>
-      <c r="AB169" s="29"/>
-      <c r="AC169" s="29"/>
-      <c r="AD169" s="29"/>
-      <c r="AE169" s="29"/>
-      <c r="AF169" s="29"/>
+      <c r="AB169" s="32"/>
+      <c r="AC169" s="32"/>
+      <c r="AD169" s="32"/>
+      <c r="AE169" s="32"/>
+      <c r="AF169" s="32"/>
       <c r="AH169" t="s">
         <v>91</v>
       </c>
@@ -60353,15 +60405,15 @@
       <c r="U170" s="5"/>
       <c r="V170" s="5"/>
       <c r="W170" s="5"/>
-      <c r="X170" s="32"/>
+      <c r="X170" s="35"/>
       <c r="Y170" s="13"/>
       <c r="Z170" s="13"/>
       <c r="AA170" s="13"/>
-      <c r="AB170" s="29"/>
-      <c r="AC170" s="29"/>
-      <c r="AD170" s="29"/>
-      <c r="AE170" s="29"/>
-      <c r="AF170" s="29"/>
+      <c r="AB170" s="32"/>
+      <c r="AC170" s="32"/>
+      <c r="AD170" s="32"/>
+      <c r="AE170" s="32"/>
+      <c r="AF170" s="32"/>
       <c r="AH170" t="s">
         <v>96</v>
       </c>
@@ -60403,15 +60455,15 @@
       <c r="U171" s="5"/>
       <c r="V171" s="5"/>
       <c r="W171" s="5"/>
-      <c r="X171" s="32"/>
+      <c r="X171" s="35"/>
       <c r="Y171" s="13"/>
       <c r="Z171" s="13"/>
       <c r="AA171" s="13"/>
-      <c r="AB171" s="29"/>
-      <c r="AC171" s="29"/>
-      <c r="AD171" s="29"/>
-      <c r="AE171" s="29"/>
-      <c r="AF171" s="29"/>
+      <c r="AB171" s="32"/>
+      <c r="AC171" s="32"/>
+      <c r="AD171" s="32"/>
+      <c r="AE171" s="32"/>
+      <c r="AF171" s="32"/>
       <c r="AH171" t="s">
         <v>100</v>
       </c>
@@ -60450,15 +60502,15 @@
       <c r="U172" s="5"/>
       <c r="V172" s="5"/>
       <c r="W172" s="5"/>
-      <c r="X172" s="32"/>
+      <c r="X172" s="35"/>
       <c r="Y172" s="13"/>
       <c r="Z172" s="13"/>
       <c r="AA172" s="13"/>
-      <c r="AB172" s="29"/>
-      <c r="AC172" s="29"/>
-      <c r="AD172" s="29"/>
-      <c r="AE172" s="29"/>
-      <c r="AF172" s="29"/>
+      <c r="AB172" s="32"/>
+      <c r="AC172" s="32"/>
+      <c r="AD172" s="32"/>
+      <c r="AE172" s="32"/>
+      <c r="AF172" s="32"/>
       <c r="AH172" t="s">
         <v>103</v>
       </c>
@@ -60497,15 +60549,15 @@
       <c r="U173" s="5"/>
       <c r="V173" s="5"/>
       <c r="W173" s="5"/>
-      <c r="X173" s="32"/>
+      <c r="X173" s="35"/>
       <c r="Y173" s="13"/>
       <c r="Z173" s="13"/>
       <c r="AA173" s="13"/>
-      <c r="AB173" s="29"/>
-      <c r="AC173" s="29"/>
-      <c r="AD173" s="29"/>
-      <c r="AE173" s="29"/>
-      <c r="AF173" s="29"/>
+      <c r="AB173" s="32"/>
+      <c r="AC173" s="32"/>
+      <c r="AD173" s="32"/>
+      <c r="AE173" s="32"/>
+      <c r="AF173" s="32"/>
     </row>
     <row r="174" ht="14.25">
       <c r="A174" s="5"/>
@@ -60541,15 +60593,15 @@
       <c r="U174" s="5"/>
       <c r="V174" s="5"/>
       <c r="W174" s="5"/>
-      <c r="X174" s="32"/>
+      <c r="X174" s="35"/>
       <c r="Y174" s="13"/>
       <c r="Z174" s="13"/>
       <c r="AA174" s="13"/>
-      <c r="AB174" s="29"/>
-      <c r="AC174" s="29"/>
-      <c r="AD174" s="29"/>
-      <c r="AE174" s="29"/>
-      <c r="AF174" s="29"/>
+      <c r="AB174" s="32"/>
+      <c r="AC174" s="32"/>
+      <c r="AD174" s="32"/>
+      <c r="AE174" s="32"/>
+      <c r="AF174" s="32"/>
     </row>
     <row r="175" ht="14.25">
       <c r="A175" s="5"/>
@@ -60585,15 +60637,15 @@
       <c r="U175" s="5"/>
       <c r="V175" s="5"/>
       <c r="W175" s="5"/>
-      <c r="X175" s="32"/>
+      <c r="X175" s="35"/>
       <c r="Y175" s="13"/>
       <c r="Z175" s="13"/>
       <c r="AA175" s="13"/>
-      <c r="AB175" s="29"/>
-      <c r="AC175" s="29"/>
-      <c r="AD175" s="29"/>
-      <c r="AE175" s="29"/>
-      <c r="AF175" s="29"/>
+      <c r="AB175" s="32"/>
+      <c r="AC175" s="32"/>
+      <c r="AD175" s="32"/>
+      <c r="AE175" s="32"/>
+      <c r="AF175" s="32"/>
     </row>
     <row r="180" ht="14.25">
       <c r="A180" s="5"/>
@@ -60645,7 +60697,7 @@
         <v>26</v>
       </c>
       <c r="AH181" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AI181" t="s">
         <v>114</v>
@@ -60870,17 +60922,17 @@
       <c r="U189" t="s">
         <v>26</v>
       </c>
-      <c r="X189" s="32"/>
+      <c r="X189" s="35"/>
       <c r="Y189" s="13"/>
       <c r="Z189" s="13"/>
       <c r="AA189" s="13"/>
-      <c r="AB189" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC189" s="29"/>
-      <c r="AD189" s="29"/>
-      <c r="AE189" s="29"/>
-      <c r="AF189" s="29"/>
+      <c r="AB189" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="AC189" s="32"/>
+      <c r="AD189" s="32"/>
+      <c r="AE189" s="32"/>
+      <c r="AF189" s="32"/>
       <c r="AI189" t="s">
         <v>127</v>
       </c>
@@ -60910,23 +60962,23 @@
       <c r="U190" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="X190" s="32"/>
+      <c r="X190" s="35"/>
       <c r="Y190" s="13"/>
       <c r="Z190" s="13"/>
       <c r="AA190" s="13"/>
-      <c r="AB190" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC190" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD190" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE190" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF190" s="29">
+      <c r="AB190" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC190" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD190" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE190" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF190" s="32">
         <v>1</v>
       </c>
       <c r="AI190" t="s">
@@ -60958,23 +61010,23 @@
       <c r="U191" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="X191" s="32"/>
+      <c r="X191" s="35"/>
       <c r="Y191" s="13"/>
       <c r="Z191" s="13"/>
       <c r="AA191" s="13"/>
-      <c r="AB191" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC191" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD191" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE191" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF191" s="29">
+      <c r="AB191" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC191" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD191" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE191" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF191" s="32">
         <v>0</v>
       </c>
       <c r="AI191" t="s">
@@ -61004,23 +61056,23 @@
         <v>122</v>
       </c>
       <c r="U192" s="6"/>
-      <c r="X192" s="32"/>
+      <c r="X192" s="35"/>
       <c r="Y192" s="13"/>
       <c r="Z192" s="13"/>
       <c r="AA192" s="13"/>
-      <c r="AB192" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC192" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD192" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE192" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF192" s="29">
+      <c r="AB192" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC192" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD192" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE192" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF192" s="32">
         <v>1</v>
       </c>
       <c r="AI192" t="s">
@@ -61050,23 +61102,23 @@
       <c r="U193" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="X193" s="32"/>
+      <c r="X193" s="35"/>
       <c r="Y193" s="13"/>
       <c r="Z193" s="13"/>
       <c r="AA193" s="13"/>
-      <c r="AB193" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC193" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD193" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE193" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF193" s="29">
+      <c r="AB193" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC193" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD193" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE193" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF193" s="32">
         <v>0</v>
       </c>
       <c r="AI193" t="s">
@@ -61098,23 +61150,23 @@
       <c r="U194" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="X194" s="32"/>
+      <c r="X194" s="35"/>
       <c r="Y194" s="13"/>
       <c r="Z194" s="13"/>
       <c r="AA194" s="13"/>
-      <c r="AB194" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC194" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD194" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE194" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF194" s="29">
+      <c r="AB194" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC194" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD194" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE194" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF194" s="32">
         <v>1</v>
       </c>
       <c r="AI194" t="s">
@@ -61146,23 +61198,23 @@
       <c r="U195" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="X195" s="32"/>
+      <c r="X195" s="35"/>
       <c r="Y195" s="13"/>
       <c r="Z195" s="13"/>
       <c r="AA195" s="13"/>
-      <c r="AB195" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC195" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD195" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE195" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF195" s="29">
+      <c r="AB195" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC195" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD195" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE195" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF195" s="32">
         <v>0</v>
       </c>
       <c r="AI195" t="s">
@@ -61192,23 +61244,23 @@
         <v>122</v>
       </c>
       <c r="U196" s="6"/>
-      <c r="X196" s="32"/>
+      <c r="X196" s="35"/>
       <c r="Y196" s="13"/>
       <c r="Z196" s="13"/>
       <c r="AA196" s="13"/>
-      <c r="AB196" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC196" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD196" s="29">
-        <v>1</v>
-      </c>
-      <c r="AE196" s="29">
-        <v>1</v>
-      </c>
-      <c r="AF196" s="29">
+      <c r="AB196" s="32">
+        <v>0</v>
+      </c>
+      <c r="AC196" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD196" s="32">
+        <v>1</v>
+      </c>
+      <c r="AE196" s="32">
+        <v>1</v>
+      </c>
+      <c r="AF196" s="32">
         <v>1</v>
       </c>
       <c r="AI196" t="s">
@@ -61302,15 +61354,15 @@
         <v>1</v>
       </c>
       <c r="U200" s="6"/>
-      <c r="AB200" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="AC200" s="29"/>
-      <c r="AD200" s="29"/>
-      <c r="AE200" s="29"/>
-      <c r="AF200" s="29"/>
+      <c r="AB200" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="AC200" s="32"/>
+      <c r="AD200" s="32"/>
+      <c r="AE200" s="32"/>
+      <c r="AF200" s="32"/>
       <c r="AI200" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="201" ht="14.25">
@@ -61333,32 +61385,32 @@
         <v>136</v>
       </c>
       <c r="U201" t="s">
-        <v>234</v>
-      </c>
-      <c r="X201" s="32"/>
+        <v>238</v>
+      </c>
+      <c r="X201" s="35"/>
       <c r="Y201" s="13"/>
       <c r="Z201" s="13"/>
       <c r="AA201" s="13"/>
-      <c r="AB201" s="29">
-        <v>1</v>
-      </c>
-      <c r="AC201" s="29">
-        <v>0</v>
-      </c>
-      <c r="AD201" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE201" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF201" s="29">
+      <c r="AB201" s="32">
+        <v>1</v>
+      </c>
+      <c r="AC201" s="32">
+        <v>0</v>
+      </c>
+      <c r="AD201" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE201" s="32">
+        <v>0</v>
+      </c>
+      <c r="AF201" s="32">
         <v>0</v>
       </c>
       <c r="AI201" t="s">
         <v>136</v>
       </c>
       <c r="AJ201" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="202" ht="14.25">
@@ -61432,7 +61484,7 @@
         <v>0</v>
       </c>
       <c r="T205" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="206" ht="14.25">
@@ -61556,12 +61608,12 @@
     </row>
     <row r="214" ht="14.25">
       <c r="AH214" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="217" ht="14.25">
       <c r="A217" s="12" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B217" s="12"/>
       <c r="C217" s="12"/>
@@ -61580,7 +61632,7 @@
       <c r="L217" s="9"/>
       <c r="M217" s="9"/>
       <c r="N217" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="O217" s="12"/>
       <c r="P217" s="12"/>
@@ -61593,21 +61645,21 @@
       <c r="U217" s="11"/>
       <c r="V217" s="11"/>
       <c r="W217" s="11"/>
-      <c r="X217" s="32" t="s">
-        <v>210</v>
+      <c r="X217" s="35" t="s">
+        <v>214</v>
       </c>
       <c r="Y217" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Z217" s="12"/>
       <c r="AA217" s="12"/>
-      <c r="AB217" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC217" s="29"/>
-      <c r="AD217" s="29"/>
-      <c r="AE217" s="29"/>
-      <c r="AF217" s="29"/>
+      <c r="AB217" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC217" s="32"/>
+      <c r="AD217" s="32"/>
+      <c r="AE217" s="32"/>
+      <c r="AF217" s="32"/>
     </row>
     <row r="218" ht="14.25">
       <c r="A218" s="5"/>
@@ -61619,7 +61671,7 @@
       <c r="G218" s="7"/>
       <c r="H218" s="7"/>
       <c r="I218" s="12" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="J218" s="12"/>
       <c r="K218" s="12"/>
@@ -61635,7 +61687,7 @@
       <c r="U218" s="12"/>
       <c r="V218" s="12"/>
       <c r="W218" s="12"/>
-      <c r="X218" s="32" t="s">
+      <c r="X218" s="35" t="s">
         <v>71</v>
       </c>
       <c r="Y218" s="8" t="s">
@@ -61644,7 +61696,7 @@
       <c r="Z218" s="8"/>
       <c r="AA218" s="8"/>
       <c r="AB218" s="12" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="AC218" s="12"/>
       <c r="AD218" s="12"/>
@@ -61654,7 +61706,7 @@
         <v>71</v>
       </c>
       <c r="AI218" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="219" ht="14.25">
@@ -61681,7 +61733,7 @@
       <c r="U219" s="12"/>
       <c r="V219" s="12"/>
       <c r="W219" s="12"/>
-      <c r="X219" s="32">
+      <c r="X219" s="35">
         <v>1</v>
       </c>
       <c r="Y219" s="8" t="s">
